--- a/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
+++ b/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
@@ -56839,7 +56839,7 @@
         </is>
       </c>
       <c r="E907" s="4" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F907" s="3" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>6739200</v>
       </c>
       <c r="I907" s="5" t="n">
-        <v>24506</v>
+        <v>24417</v>
       </c>
       <c r="J907" s="3" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>6739200</v>
       </c>
       <c r="L907" s="5" t="n">
-        <v>24506</v>
+        <v>24417</v>
       </c>
       <c r="M907" s="3" t="inlineStr">
         <is>
@@ -81846,9 +81846,9 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>D | 275呎 (开放式)
+          <t>D | 276呎 (开放式)
 $674万
-$24,506/呎
+$24,417/呎
 (19年-10月-15日)</t>
         </is>
       </c>

--- a/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
+++ b/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>9464300</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>25038</v>
+        <v>24972</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>9464300</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>25038</v>
+        <v>24972</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -73880,9 +73880,9 @@
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>H | 378呎 (1房)
+          <t>H | 379呎 (1房)
 $946万
-$25,038/呎
+$24,972/呎
 (19年-10月-23日)</t>
         </is>
       </c>

--- a/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
+++ b/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>32234400</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>26400</v>
+        <v>26378</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>32234400</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>26400</v>
+        <v>26378</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -75720,9 +75720,9 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>A | 1221呎 (4+房)
+          <t>A | 1222呎 (4+房)
 $3223万
-$26,400/呎
+$26,378/呎
 (19年-11月-12日)</t>
         </is>
       </c>

--- a/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
+++ b/九龙-西南九龙-汇玺III/汇玺III_销控明细表.xlsx
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>9602100</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>25335</v>
+        <v>25402</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>9602100</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>25335</v>
+        <v>25402</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>9299000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>24536</v>
+        <v>24601</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>9299000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>24536</v>
+        <v>24601</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>9464300</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>24972</v>
+        <v>25038</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>9464300</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>24972</v>
+        <v>25038</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>9111000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>24040</v>
+        <v>24103</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>9111000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>24040</v>
+        <v>24103</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>9025800</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>23815</v>
+        <v>23878</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>9025800</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>23815</v>
+        <v>23878</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>9002200</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>23753</v>
+        <v>23815</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>9002200</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>23753</v>
+        <v>23815</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>9229000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>24351</v>
+        <v>24415</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>9229000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>24351</v>
+        <v>24415</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>8579000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>22636</v>
+        <v>22696</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>8579000</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>22636</v>
+        <v>22696</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>8543000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>22541</v>
+        <v>22601</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>8543000</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>22541</v>
+        <v>22601</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>8850200</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>23351</v>
+        <v>23413</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>8850200</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>23351</v>
+        <v>23413</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>8996900</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>23739</v>
+        <v>23801</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>8996900</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>23739</v>
+        <v>23801</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>8329400</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>21977</v>
+        <v>22035</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>8329400</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>21977</v>
+        <v>22035</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>8369200</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>22082</v>
+        <v>22141</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>8369200</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>22082</v>
+        <v>22141</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>8383300</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>22120</v>
+        <v>22178</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>8383300</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>22120</v>
+        <v>22178</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>8229400</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>21713</v>
+        <v>21771</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>8229400</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>21713</v>
+        <v>21771</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>8308000</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>21921</v>
+        <v>21979</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>8308000</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>21921</v>
+        <v>21979</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>8179000</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>21580</v>
+        <v>21638</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>8179000</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>21580</v>
+        <v>21638</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>8528000</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>22501</v>
+        <v>22561</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>8528000</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>22501</v>
+        <v>22561</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>8305200</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>21913</v>
+        <v>21971</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>8305200</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>21913</v>
+        <v>21971</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>33943800</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>27777</v>
+        <v>27800</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>33943800</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>27777</v>
+        <v>27800</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>8048600</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>21236</v>
+        <v>21293</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>8048600</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>21236</v>
+        <v>21293</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>33089800</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>27078</v>
+        <v>27101</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>33089800</v>
       </c>
       <c r="L236" s="5" t="n">
-        <v>27078</v>
+        <v>27101</v>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>8007000</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>21127</v>
+        <v>21183</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>8007000</v>
       </c>
       <c r="L238" s="5" t="n">
-        <v>21127</v>
+        <v>21183</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>32234400</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>26378</v>
+        <v>26400</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>32234400</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>26378</v>
+        <v>26400</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>32300000</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>26432</v>
+        <v>26454</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>32300000</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>26432</v>
+        <v>26454</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E263" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>32488000</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>26586</v>
+        <v>26608</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>32488000</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>26586</v>
+        <v>26608</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>7847000</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>20704</v>
+        <v>20759</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>7847000</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>20704</v>
+        <v>20759</v>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>32288000</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>26422</v>
+        <v>26444</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>32288000</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>26422</v>
+        <v>26444</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         </is>
       </c>
       <c r="E283" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>8003900</v>
       </c>
       <c r="I283" s="5" t="n">
-        <v>21118</v>
+        <v>21174</v>
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>8003900</v>
       </c>
       <c r="L283" s="5" t="n">
-        <v>21118</v>
+        <v>21174</v>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>31929150</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>26129</v>
+        <v>26150</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>31929150</v>
       </c>
       <c r="L290" s="5" t="n">
-        <v>26129</v>
+        <v>26150</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>8082200</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>21325</v>
+        <v>21381</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>8082200</v>
       </c>
       <c r="L292" s="5" t="n">
-        <v>21325</v>
+        <v>21381</v>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         </is>
       </c>
       <c r="E310" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>7729400</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>20394</v>
+        <v>20448</v>
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>7729400</v>
       </c>
       <c r="L310" s="5" t="n">
-        <v>20394</v>
+        <v>20448</v>
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>10199500</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>26912</v>
+        <v>26983</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>10199500</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>26912</v>
+        <v>26983</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         </is>
       </c>
       <c r="E326" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>31300000</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>25614</v>
+        <v>25635</v>
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>31300000</v>
       </c>
       <c r="L326" s="5" t="n">
-        <v>25614</v>
+        <v>25635</v>
       </c>
       <c r="M326" s="3" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         </is>
       </c>
       <c r="E328" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>8227700</v>
       </c>
       <c r="I328" s="5" t="n">
-        <v>21709</v>
+        <v>21766</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>8227700</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>21709</v>
+        <v>21766</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         </is>
       </c>
       <c r="E337" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>8016600</v>
       </c>
       <c r="I337" s="5" t="n">
-        <v>21152</v>
+        <v>21208</v>
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>8016600</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>21152</v>
+        <v>21208</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         </is>
       </c>
       <c r="E344" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>29800000</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>24386</v>
+        <v>24406</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>29800000</v>
       </c>
       <c r="L344" s="5" t="n">
-        <v>24386</v>
+        <v>24406</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="E346" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>7795300</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>20568</v>
+        <v>20622</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>7795300</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>20568</v>
+        <v>20622</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         </is>
       </c>
       <c r="E355" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>7787200</v>
       </c>
       <c r="I355" s="5" t="n">
-        <v>20547</v>
+        <v>20601</v>
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>7787200</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>20547</v>
+        <v>20601</v>
       </c>
       <c r="M355" s="3" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         </is>
       </c>
       <c r="E364" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>7652200</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>20191</v>
+        <v>20244</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>7652200</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>20191</v>
+        <v>20244</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         </is>
       </c>
       <c r="E371" s="4" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>29300000</v>
       </c>
       <c r="I371" s="5" t="n">
-        <v>23977</v>
+        <v>23997</v>
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>29300000</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>23977</v>
+        <v>23997</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         </is>
       </c>
       <c r="E373" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>7674200</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>20249</v>
+        <v>20302</v>
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>7674200</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>20249</v>
+        <v>20302</v>
       </c>
       <c r="M373" s="3" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>7763700</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>20485</v>
+        <v>20539</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>7763700</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>20485</v>
+        <v>20539</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         </is>
       </c>
       <c r="E391" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>7852200</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>20718</v>
+        <v>20773</v>
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>7852200</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>20718</v>
+        <v>20773</v>
       </c>
       <c r="M391" s="3" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         </is>
       </c>
       <c r="E406" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>15893400</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>30158</v>
+        <v>30101</v>
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>15893400</v>
       </c>
       <c r="L406" s="5" t="n">
-        <v>30158</v>
+        <v>30101</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         </is>
       </c>
       <c r="E409" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>53800000</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>35535</v>
+        <v>35558</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>53800000</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>35535</v>
+        <v>35558</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         </is>
       </c>
       <c r="E425" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>8588200</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>24468</v>
+        <v>24538</v>
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>8588200</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>24468</v>
+        <v>24538</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         </is>
       </c>
       <c r="E431" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>53106300</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>35077</v>
+        <v>35100</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>53106300</v>
       </c>
       <c r="L431" s="5" t="n">
-        <v>35077</v>
+        <v>35100</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         </is>
       </c>
       <c r="E436" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>8283000</v>
       </c>
       <c r="I436" s="5" t="n">
-        <v>23598</v>
+        <v>23666</v>
       </c>
       <c r="J436" s="3" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>8283000</v>
       </c>
       <c r="L436" s="5" t="n">
-        <v>23598</v>
+        <v>23666</v>
       </c>
       <c r="M436" s="3" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>15789000</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>29960</v>
+        <v>29903</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>15789000</v>
       </c>
       <c r="L439" s="5" t="n">
-        <v>29960</v>
+        <v>29903</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         </is>
       </c>
       <c r="E442" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>52198500</v>
       </c>
       <c r="I442" s="5" t="n">
-        <v>34477</v>
+        <v>34500</v>
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>52198500</v>
       </c>
       <c r="L442" s="5" t="n">
-        <v>34477</v>
+        <v>34500</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         </is>
       </c>
       <c r="E447" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>8317700</v>
       </c>
       <c r="I447" s="5" t="n">
-        <v>23697</v>
+        <v>23765</v>
       </c>
       <c r="J447" s="3" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>8317700</v>
       </c>
       <c r="L447" s="5" t="n">
-        <v>23697</v>
+        <v>23765</v>
       </c>
       <c r="M447" s="3" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         </is>
       </c>
       <c r="E450" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>15687400</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>29767</v>
+        <v>29711</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>15687400</v>
       </c>
       <c r="L450" s="5" t="n">
-        <v>29767</v>
+        <v>29711</v>
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         </is>
       </c>
       <c r="E453" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>51895900</v>
       </c>
       <c r="I453" s="5" t="n">
-        <v>34277</v>
+        <v>34300</v>
       </c>
       <c r="J453" s="3" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>51895900</v>
       </c>
       <c r="L453" s="5" t="n">
-        <v>34277</v>
+        <v>34300</v>
       </c>
       <c r="M453" s="3" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         </is>
       </c>
       <c r="E458" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>8248800</v>
       </c>
       <c r="I458" s="5" t="n">
-        <v>23501</v>
+        <v>23568</v>
       </c>
       <c r="J458" s="3" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>8248800</v>
       </c>
       <c r="L458" s="5" t="n">
-        <v>23501</v>
+        <v>23568</v>
       </c>
       <c r="M458" s="3" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="E464" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>57494000</v>
       </c>
       <c r="I464" s="5" t="n">
-        <v>37975</v>
+        <v>38000</v>
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>57494000</v>
       </c>
       <c r="L464" s="5" t="n">
-        <v>37975</v>
+        <v>38000</v>
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         </is>
       </c>
       <c r="E469" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>8145400</v>
       </c>
       <c r="I469" s="5" t="n">
-        <v>23206</v>
+        <v>23273</v>
       </c>
       <c r="J469" s="3" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>8145400</v>
       </c>
       <c r="L469" s="5" t="n">
-        <v>23206</v>
+        <v>23273</v>
       </c>
       <c r="M469" s="3" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         </is>
       </c>
       <c r="E475" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>54360000</v>
       </c>
       <c r="I475" s="5" t="n">
-        <v>35905</v>
+        <v>35929</v>
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>54360000</v>
       </c>
       <c r="L475" s="5" t="n">
-        <v>35905</v>
+        <v>35929</v>
       </c>
       <c r="M475" s="3" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         </is>
       </c>
       <c r="E480" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>8110200</v>
       </c>
       <c r="I480" s="5" t="n">
-        <v>23106</v>
+        <v>23172</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>8110200</v>
       </c>
       <c r="L480" s="5" t="n">
-        <v>23106</v>
+        <v>23172</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         </is>
       </c>
       <c r="E494" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>14859200</v>
       </c>
       <c r="I494" s="5" t="n">
-        <v>28196</v>
+        <v>28142</v>
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>14859200</v>
       </c>
       <c r="L494" s="5" t="n">
-        <v>28196</v>
+        <v>28142</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         </is>
       </c>
       <c r="E513" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>8008600</v>
       </c>
       <c r="I513" s="5" t="n">
-        <v>22817</v>
+        <v>22882</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>8008600</v>
       </c>
       <c r="L513" s="5" t="n">
-        <v>22817</v>
+        <v>22882</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         </is>
       </c>
       <c r="E516" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>14680000</v>
       </c>
       <c r="I516" s="5" t="n">
-        <v>27856</v>
+        <v>27803</v>
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>14680000</v>
       </c>
       <c r="L516" s="5" t="n">
-        <v>27856</v>
+        <v>27803</v>
       </c>
       <c r="M516" s="3" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         </is>
       </c>
       <c r="E519" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F519" s="3" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>43438600</v>
       </c>
       <c r="I519" s="5" t="n">
-        <v>28691</v>
+        <v>28710</v>
       </c>
       <c r="J519" s="3" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>43438600</v>
       </c>
       <c r="L519" s="5" t="n">
-        <v>28691</v>
+        <v>28710</v>
       </c>
       <c r="M519" s="3" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         </is>
       </c>
       <c r="E524" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F524" s="3" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>7944200</v>
       </c>
       <c r="I524" s="5" t="n">
-        <v>22633</v>
+        <v>22698</v>
       </c>
       <c r="J524" s="3" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>7944200</v>
       </c>
       <c r="L524" s="5" t="n">
-        <v>22633</v>
+        <v>22698</v>
       </c>
       <c r="M524" s="3" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         </is>
       </c>
       <c r="E527" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F527" s="3" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>15531500</v>
       </c>
       <c r="I527" s="5" t="n">
-        <v>29472</v>
+        <v>29416</v>
       </c>
       <c r="J527" s="3" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>15531500</v>
       </c>
       <c r="L527" s="5" t="n">
-        <v>29472</v>
+        <v>29416</v>
       </c>
       <c r="M527" s="3" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         </is>
       </c>
       <c r="E530" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F530" s="3" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>43265600</v>
       </c>
       <c r="I530" s="5" t="n">
-        <v>28577</v>
+        <v>28596</v>
       </c>
       <c r="J530" s="3" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>43265600</v>
       </c>
       <c r="L530" s="5" t="n">
-        <v>28577</v>
+        <v>28596</v>
       </c>
       <c r="M530" s="3" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         </is>
       </c>
       <c r="E535" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>7944200</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>22633</v>
+        <v>22698</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>7944200</v>
       </c>
       <c r="L535" s="5" t="n">
-        <v>22633</v>
+        <v>22698</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         </is>
       </c>
       <c r="E541" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F541" s="3" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>42210400</v>
       </c>
       <c r="I541" s="5" t="n">
-        <v>27880</v>
+        <v>27898</v>
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>42210400</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>27880</v>
+        <v>27898</v>
       </c>
       <c r="M541" s="3" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         </is>
       </c>
       <c r="E546" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F546" s="3" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>7926200</v>
       </c>
       <c r="I546" s="5" t="n">
-        <v>22582</v>
+        <v>22646</v>
       </c>
       <c r="J546" s="3" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>7926200</v>
       </c>
       <c r="L546" s="5" t="n">
-        <v>22582</v>
+        <v>22646</v>
       </c>
       <c r="M546" s="3" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         </is>
       </c>
       <c r="E552" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>42440700</v>
       </c>
       <c r="I552" s="5" t="n">
-        <v>28032</v>
+        <v>28051</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>42440700</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>28032</v>
+        <v>28051</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         </is>
       </c>
       <c r="E557" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>8071500</v>
       </c>
       <c r="I557" s="5" t="n">
-        <v>22996</v>
+        <v>23061</v>
       </c>
       <c r="J557" s="3" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>8071500</v>
       </c>
       <c r="L557" s="5" t="n">
-        <v>22996</v>
+        <v>23061</v>
       </c>
       <c r="M557" s="3" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         </is>
       </c>
       <c r="E568" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F568" s="3" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>7879000</v>
       </c>
       <c r="I568" s="5" t="n">
-        <v>22447</v>
+        <v>22511</v>
       </c>
       <c r="J568" s="3" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>7879000</v>
       </c>
       <c r="L568" s="5" t="n">
-        <v>22447</v>
+        <v>22511</v>
       </c>
       <c r="M568" s="3" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         </is>
       </c>
       <c r="E579" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F579" s="3" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>7824200</v>
       </c>
       <c r="I579" s="5" t="n">
-        <v>22291</v>
+        <v>22355</v>
       </c>
       <c r="J579" s="3" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>7824200</v>
       </c>
       <c r="L579" s="5" t="n">
-        <v>22291</v>
+        <v>22355</v>
       </c>
       <c r="M579" s="3" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         </is>
       </c>
       <c r="E593" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F593" s="3" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>14240600</v>
       </c>
       <c r="I593" s="5" t="n">
-        <v>27022</v>
+        <v>26971</v>
       </c>
       <c r="J593" s="3" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>14240600</v>
       </c>
       <c r="L593" s="5" t="n">
-        <v>27022</v>
+        <v>26971</v>
       </c>
       <c r="M593" s="3" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         </is>
       </c>
       <c r="E596" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F596" s="3" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>41262400</v>
       </c>
       <c r="I596" s="5" t="n">
-        <v>27254</v>
+        <v>27272</v>
       </c>
       <c r="J596" s="3" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>41262400</v>
       </c>
       <c r="L596" s="5" t="n">
-        <v>27254</v>
+        <v>27272</v>
       </c>
       <c r="M596" s="3" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         </is>
       </c>
       <c r="E601" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F601" s="3" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>7808600</v>
       </c>
       <c r="I601" s="5" t="n">
-        <v>22247</v>
+        <v>22310</v>
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>7808600</v>
       </c>
       <c r="L601" s="5" t="n">
-        <v>22247</v>
+        <v>22310</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         </is>
       </c>
       <c r="E612" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F612" s="3" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>7783000</v>
       </c>
       <c r="I612" s="5" t="n">
-        <v>22174</v>
+        <v>22237</v>
       </c>
       <c r="J612" s="3" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>7783000</v>
       </c>
       <c r="L612" s="5" t="n">
-        <v>22174</v>
+        <v>22237</v>
       </c>
       <c r="M612" s="3" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         </is>
       </c>
       <c r="E615" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F615" s="3" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>14327100</v>
       </c>
       <c r="I615" s="5" t="n">
-        <v>27186</v>
+        <v>27135</v>
       </c>
       <c r="J615" s="3" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>14327100</v>
       </c>
       <c r="L615" s="5" t="n">
-        <v>27186</v>
+        <v>27135</v>
       </c>
       <c r="M615" s="3" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         </is>
       </c>
       <c r="E623" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F623" s="3" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>7830400</v>
       </c>
       <c r="I623" s="5" t="n">
-        <v>22309</v>
+        <v>22373</v>
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>7830400</v>
       </c>
       <c r="L623" s="5" t="n">
-        <v>22309</v>
+        <v>22373</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         </is>
       </c>
       <c r="E628" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F628" s="3" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>9476800</v>
       </c>
       <c r="I628" s="5" t="n">
-        <v>26324</v>
+        <v>26398</v>
       </c>
       <c r="J628" s="3" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>9476800</v>
       </c>
       <c r="L628" s="5" t="n">
-        <v>26324</v>
+        <v>26398</v>
       </c>
       <c r="M628" s="3" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         </is>
       </c>
       <c r="E634" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F634" s="3" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>7858400</v>
       </c>
       <c r="I634" s="5" t="n">
-        <v>22389</v>
+        <v>22453</v>
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>7858400</v>
       </c>
       <c r="L634" s="5" t="n">
-        <v>22389</v>
+        <v>22453</v>
       </c>
       <c r="M634" s="3" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         </is>
       </c>
       <c r="E637" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F637" s="3" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>14869800</v>
       </c>
       <c r="I637" s="5" t="n">
-        <v>28216</v>
+        <v>28162</v>
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>14869800</v>
       </c>
       <c r="L637" s="5" t="n">
-        <v>28216</v>
+        <v>28162</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         </is>
       </c>
       <c r="E640" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F640" s="3" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>41177100</v>
       </c>
       <c r="I640" s="5" t="n">
-        <v>27144</v>
+        <v>27180</v>
       </c>
       <c r="J640" s="3" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>41177100</v>
       </c>
       <c r="L640" s="5" t="n">
-        <v>27144</v>
+        <v>27180</v>
       </c>
       <c r="M640" s="3" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         </is>
       </c>
       <c r="E648" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F648" s="3" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>14299400</v>
       </c>
       <c r="I648" s="5" t="n">
-        <v>27134</v>
+        <v>27082</v>
       </c>
       <c r="J648" s="3" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>14299400</v>
       </c>
       <c r="L648" s="5" t="n">
-        <v>27134</v>
+        <v>27082</v>
       </c>
       <c r="M648" s="3" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="E650" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F650" s="3" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>9547100</v>
       </c>
       <c r="I650" s="5" t="n">
-        <v>26520</v>
+        <v>26594</v>
       </c>
       <c r="J650" s="3" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>9547100</v>
       </c>
       <c r="L650" s="5" t="n">
-        <v>26520</v>
+        <v>26594</v>
       </c>
       <c r="M650" s="3" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="E651" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F651" s="3" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>40163200</v>
       </c>
       <c r="I651" s="5" t="n">
-        <v>26475</v>
+        <v>26510</v>
       </c>
       <c r="J651" s="3" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>40163200</v>
       </c>
       <c r="L651" s="5" t="n">
-        <v>26475</v>
+        <v>26510</v>
       </c>
       <c r="M651" s="3" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         </is>
       </c>
       <c r="E656" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F656" s="3" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>7709400</v>
       </c>
       <c r="I656" s="5" t="n">
-        <v>21964</v>
+        <v>22027</v>
       </c>
       <c r="J656" s="3" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>7709400</v>
       </c>
       <c r="L656" s="5" t="n">
-        <v>21964</v>
+        <v>22027</v>
       </c>
       <c r="M656" s="3" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         </is>
       </c>
       <c r="E659" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F659" s="3" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>15586400</v>
       </c>
       <c r="I659" s="5" t="n">
-        <v>29576</v>
+        <v>29520</v>
       </c>
       <c r="J659" s="3" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>15586400</v>
       </c>
       <c r="L659" s="5" t="n">
-        <v>29576</v>
+        <v>29520</v>
       </c>
       <c r="M659" s="3" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         </is>
       </c>
       <c r="E661" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F661" s="3" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>10411200</v>
       </c>
       <c r="I661" s="5" t="n">
-        <v>28920</v>
+        <v>29001</v>
       </c>
       <c r="J661" s="3" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>10411200</v>
       </c>
       <c r="L661" s="5" t="n">
-        <v>28920</v>
+        <v>29001</v>
       </c>
       <c r="M661" s="3" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         </is>
       </c>
       <c r="E667" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F667" s="3" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>7604600</v>
       </c>
       <c r="I667" s="5" t="n">
-        <v>21666</v>
+        <v>21727</v>
       </c>
       <c r="J667" s="3" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>7604600</v>
       </c>
       <c r="L667" s="5" t="n">
-        <v>21666</v>
+        <v>21727</v>
       </c>
       <c r="M667" s="3" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         </is>
       </c>
       <c r="E673" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F673" s="3" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>40298300</v>
       </c>
       <c r="I673" s="5" t="n">
-        <v>26564</v>
+        <v>26600</v>
       </c>
       <c r="J673" s="3" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>40298300</v>
       </c>
       <c r="L673" s="5" t="n">
-        <v>26564</v>
+        <v>26600</v>
       </c>
       <c r="M673" s="3" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         </is>
       </c>
       <c r="E678" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F678" s="3" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>7566200</v>
       </c>
       <c r="I678" s="5" t="n">
-        <v>21556</v>
+        <v>21618</v>
       </c>
       <c r="J678" s="3" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>7566200</v>
       </c>
       <c r="L678" s="5" t="n">
-        <v>21556</v>
+        <v>21618</v>
       </c>
       <c r="M678" s="3" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         </is>
       </c>
       <c r="E684" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F684" s="3" t="inlineStr">
         <is>
@@ -43021,7 +43021,7 @@
         <v>40036600</v>
       </c>
       <c r="I684" s="5" t="n">
-        <v>26392</v>
+        <v>26427</v>
       </c>
       <c r="J684" s="3" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>40036600</v>
       </c>
       <c r="L684" s="5" t="n">
-        <v>26392</v>
+        <v>26427</v>
       </c>
       <c r="M684" s="3" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         </is>
       </c>
       <c r="E689" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F689" s="3" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>7598400</v>
       </c>
       <c r="I689" s="5" t="n">
-        <v>21648</v>
+        <v>21710</v>
       </c>
       <c r="J689" s="3" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>7598400</v>
       </c>
       <c r="L689" s="5" t="n">
-        <v>21648</v>
+        <v>21710</v>
       </c>
       <c r="M689" s="3" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         </is>
       </c>
       <c r="E692" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F692" s="3" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>14268200</v>
       </c>
       <c r="I692" s="5" t="n">
-        <v>27074</v>
+        <v>27023</v>
       </c>
       <c r="J692" s="3" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>14268200</v>
       </c>
       <c r="L692" s="5" t="n">
-        <v>27074</v>
+        <v>27023</v>
       </c>
       <c r="M692" s="3" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         </is>
       </c>
       <c r="E703" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>13568900</v>
       </c>
       <c r="I703" s="5" t="n">
-        <v>25747</v>
+        <v>25699</v>
       </c>
       <c r="J703" s="3" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>13568900</v>
       </c>
       <c r="L703" s="5" t="n">
-        <v>25747</v>
+        <v>25699</v>
       </c>
       <c r="M703" s="3" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         </is>
       </c>
       <c r="E705" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F705" s="3" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>9058900</v>
       </c>
       <c r="I705" s="5" t="n">
-        <v>25164</v>
+        <v>25234</v>
       </c>
       <c r="J705" s="3" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>9058900</v>
       </c>
       <c r="L705" s="5" t="n">
-        <v>25164</v>
+        <v>25234</v>
       </c>
       <c r="M705" s="3" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         </is>
       </c>
       <c r="E711" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F711" s="3" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>7603800</v>
       </c>
       <c r="I711" s="5" t="n">
-        <v>21663</v>
+        <v>21725</v>
       </c>
       <c r="J711" s="3" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>7603800</v>
       </c>
       <c r="L711" s="5" t="n">
-        <v>21663</v>
+        <v>21725</v>
       </c>
       <c r="M711" s="3" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         </is>
       </c>
       <c r="E714" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F714" s="3" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>13238600</v>
       </c>
       <c r="I714" s="5" t="n">
-        <v>25121</v>
+        <v>25073</v>
       </c>
       <c r="J714" s="3" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>13238600</v>
       </c>
       <c r="L714" s="5" t="n">
-        <v>25121</v>
+        <v>25073</v>
       </c>
       <c r="M714" s="3" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         </is>
       </c>
       <c r="E717" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F717" s="3" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>39208800</v>
       </c>
       <c r="I717" s="5" t="n">
-        <v>25846</v>
+        <v>25880</v>
       </c>
       <c r="J717" s="3" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>39208800</v>
       </c>
       <c r="L717" s="5" t="n">
-        <v>25846</v>
+        <v>25880</v>
       </c>
       <c r="M717" s="3" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         </is>
       </c>
       <c r="E725" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F725" s="3" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>13238600</v>
       </c>
       <c r="I725" s="5" t="n">
-        <v>25121</v>
+        <v>25073</v>
       </c>
       <c r="J725" s="3" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>13238600</v>
       </c>
       <c r="L725" s="5" t="n">
-        <v>25121</v>
+        <v>25073</v>
       </c>
       <c r="M725" s="3" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         </is>
       </c>
       <c r="E728" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F728" s="3" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>38152800</v>
       </c>
       <c r="I728" s="5" t="n">
-        <v>25150</v>
+        <v>25183</v>
       </c>
       <c r="J728" s="3" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>38152800</v>
       </c>
       <c r="L728" s="5" t="n">
-        <v>25150</v>
+        <v>25183</v>
       </c>
       <c r="M728" s="3" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         </is>
       </c>
       <c r="E733" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>7755400</v>
       </c>
       <c r="I733" s="5" t="n">
-        <v>22095</v>
+        <v>22158</v>
       </c>
       <c r="J733" s="3" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>7755400</v>
       </c>
       <c r="L733" s="5" t="n">
-        <v>22095</v>
+        <v>22158</v>
       </c>
       <c r="M733" s="3" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         </is>
       </c>
       <c r="E738" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F738" s="3" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>8734000</v>
       </c>
       <c r="I738" s="5" t="n">
-        <v>24261</v>
+        <v>24329</v>
       </c>
       <c r="J738" s="3" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>8734000</v>
       </c>
       <c r="L738" s="5" t="n">
-        <v>24261</v>
+        <v>24329</v>
       </c>
       <c r="M738" s="3" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         </is>
       </c>
       <c r="E739" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F739" s="3" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>37558400</v>
       </c>
       <c r="I739" s="5" t="n">
-        <v>24758</v>
+        <v>24791</v>
       </c>
       <c r="J739" s="3" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>37558400</v>
       </c>
       <c r="L739" s="5" t="n">
-        <v>24758</v>
+        <v>24791</v>
       </c>
       <c r="M739" s="3" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         </is>
       </c>
       <c r="E744" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F744" s="3" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>7500400</v>
       </c>
       <c r="I744" s="5" t="n">
-        <v>21369</v>
+        <v>21430</v>
       </c>
       <c r="J744" s="3" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>7500400</v>
       </c>
       <c r="L744" s="5" t="n">
-        <v>21369</v>
+        <v>21430</v>
       </c>
       <c r="M744" s="3" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         </is>
       </c>
       <c r="E749" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F749" s="3" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>8628700</v>
       </c>
       <c r="I749" s="5" t="n">
-        <v>23969</v>
+        <v>24035</v>
       </c>
       <c r="J749" s="3" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>8628700</v>
       </c>
       <c r="L749" s="5" t="n">
-        <v>23969</v>
+        <v>24035</v>
       </c>
       <c r="M749" s="3" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         </is>
       </c>
       <c r="E750" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F750" s="3" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>37430000</v>
       </c>
       <c r="I750" s="5" t="n">
-        <v>24674</v>
+        <v>24706</v>
       </c>
       <c r="J750" s="3" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>37430000</v>
       </c>
       <c r="L750" s="5" t="n">
-        <v>24674</v>
+        <v>24706</v>
       </c>
       <c r="M750" s="3" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         </is>
       </c>
       <c r="E755" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F755" s="3" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>7399000</v>
       </c>
       <c r="I755" s="5" t="n">
-        <v>21080</v>
+        <v>21140</v>
       </c>
       <c r="J755" s="3" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>7399000</v>
       </c>
       <c r="L755" s="5" t="n">
-        <v>21080</v>
+        <v>21140</v>
       </c>
       <c r="M755" s="3" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         </is>
       </c>
       <c r="E758" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F758" s="3" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>13308200</v>
       </c>
       <c r="I758" s="5" t="n">
-        <v>25253</v>
+        <v>25205</v>
       </c>
       <c r="J758" s="3" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>13308200</v>
       </c>
       <c r="L758" s="5" t="n">
-        <v>25253</v>
+        <v>25205</v>
       </c>
       <c r="M758" s="3" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         </is>
       </c>
       <c r="E766" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F766" s="3" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>7637300</v>
       </c>
       <c r="I766" s="5" t="n">
-        <v>21759</v>
+        <v>21821</v>
       </c>
       <c r="J766" s="3" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>7637300</v>
       </c>
       <c r="L766" s="5" t="n">
-        <v>21759</v>
+        <v>21821</v>
       </c>
       <c r="M766" s="3" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         </is>
       </c>
       <c r="E771" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F771" s="3" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
         <v>8386400</v>
       </c>
       <c r="I771" s="5" t="n">
-        <v>23296</v>
+        <v>23360</v>
       </c>
       <c r="J771" s="3" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>8386400</v>
       </c>
       <c r="L771" s="5" t="n">
-        <v>23296</v>
+        <v>23360</v>
       </c>
       <c r="M771" s="3" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         </is>
       </c>
       <c r="E777" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F777" s="3" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>7541700</v>
       </c>
       <c r="I777" s="5" t="n">
-        <v>21486</v>
+        <v>21548</v>
       </c>
       <c r="J777" s="3" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>7541700</v>
       </c>
       <c r="L777" s="5" t="n">
-        <v>21486</v>
+        <v>21548</v>
       </c>
       <c r="M777" s="3" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         </is>
       </c>
       <c r="E782" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F782" s="3" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>8216600</v>
       </c>
       <c r="I782" s="5" t="n">
-        <v>22824</v>
+        <v>22887</v>
       </c>
       <c r="J782" s="3" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>8216600</v>
       </c>
       <c r="L782" s="5" t="n">
-        <v>22824</v>
+        <v>22887</v>
       </c>
       <c r="M782" s="3" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         </is>
       </c>
       <c r="E788" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F788" s="3" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>7470400</v>
       </c>
       <c r="I788" s="5" t="n">
-        <v>21283</v>
+        <v>21344</v>
       </c>
       <c r="J788" s="3" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>7470400</v>
       </c>
       <c r="L788" s="5" t="n">
-        <v>21283</v>
+        <v>21344</v>
       </c>
       <c r="M788" s="3" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         </is>
       </c>
       <c r="E791" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F791" s="3" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>12158600</v>
       </c>
       <c r="I791" s="5" t="n">
-        <v>23071</v>
+        <v>23028</v>
       </c>
       <c r="J791" s="3" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>12158600</v>
       </c>
       <c r="L791" s="5" t="n">
-        <v>23071</v>
+        <v>23028</v>
       </c>
       <c r="M791" s="3" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         </is>
       </c>
       <c r="E793" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F793" s="3" t="inlineStr">
         <is>
@@ -49779,7 +49779,7 @@
         <v>8219700</v>
       </c>
       <c r="I793" s="5" t="n">
-        <v>22832</v>
+        <v>22896</v>
       </c>
       <c r="J793" s="3" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>8219700</v>
       </c>
       <c r="L793" s="5" t="n">
-        <v>22832</v>
+        <v>22896</v>
       </c>
       <c r="M793" s="3" t="inlineStr">
         <is>
@@ -49825,7 +49825,7 @@
         </is>
       </c>
       <c r="E794" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F794" s="3" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>36814500</v>
       </c>
       <c r="I794" s="5" t="n">
-        <v>24268</v>
+        <v>24300</v>
       </c>
       <c r="J794" s="3" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>36814500</v>
       </c>
       <c r="L794" s="5" t="n">
-        <v>24268</v>
+        <v>24300</v>
       </c>
       <c r="M794" s="3" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         </is>
       </c>
       <c r="E799" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F799" s="3" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>7518200</v>
       </c>
       <c r="I799" s="5" t="n">
-        <v>21419</v>
+        <v>21481</v>
       </c>
       <c r="J799" s="3" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>7518200</v>
       </c>
       <c r="L799" s="5" t="n">
-        <v>21419</v>
+        <v>21481</v>
       </c>
       <c r="M799" s="3" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         </is>
       </c>
       <c r="E815" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F815" s="3" t="inlineStr">
         <is>
@@ -51143,7 +51143,7 @@
         <v>8120100</v>
       </c>
       <c r="I815" s="5" t="n">
-        <v>22556</v>
+        <v>22619</v>
       </c>
       <c r="J815" s="3" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>8120100</v>
       </c>
       <c r="L815" s="5" t="n">
-        <v>22556</v>
+        <v>22619</v>
       </c>
       <c r="M815" s="3" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         </is>
       </c>
       <c r="E816" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F816" s="3" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>38278900</v>
       </c>
       <c r="I816" s="5" t="n">
-        <v>25233</v>
+        <v>25267</v>
       </c>
       <c r="J816" s="3" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>38278900</v>
       </c>
       <c r="L816" s="5" t="n">
-        <v>25233</v>
+        <v>25267</v>
       </c>
       <c r="M816" s="3" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         </is>
       </c>
       <c r="E826" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F826" s="3" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>7922200</v>
       </c>
       <c r="I826" s="5" t="n">
-        <v>22006</v>
+        <v>22067</v>
       </c>
       <c r="J826" s="3" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>7922200</v>
       </c>
       <c r="L826" s="5" t="n">
-        <v>22006</v>
+        <v>22067</v>
       </c>
       <c r="M826" s="3" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         </is>
       </c>
       <c r="E827" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F827" s="3" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         <v>36460000</v>
       </c>
       <c r="I827" s="5" t="n">
-        <v>24034</v>
+        <v>24066</v>
       </c>
       <c r="J827" s="3" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>36460000</v>
       </c>
       <c r="L827" s="5" t="n">
-        <v>24034</v>
+        <v>24066</v>
       </c>
       <c r="M827" s="3" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         </is>
       </c>
       <c r="E832" s="4" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F832" s="3" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>7409700</v>
       </c>
       <c r="I832" s="5" t="n">
-        <v>21110</v>
+        <v>21171</v>
       </c>
       <c r="J832" s="3" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>7409700</v>
       </c>
       <c r="L832" s="5" t="n">
-        <v>21110</v>
+        <v>21171</v>
       </c>
       <c r="M832" s="3" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         </is>
       </c>
       <c r="E835" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F835" s="3" t="inlineStr">
         <is>
@@ -52383,7 +52383,7 @@
         <v>11970900</v>
       </c>
       <c r="I835" s="5" t="n">
-        <v>22715</v>
+        <v>22672</v>
       </c>
       <c r="J835" s="3" t="inlineStr">
         <is>
@@ -52394,7 +52394,7 @@
         <v>11970900</v>
       </c>
       <c r="L835" s="5" t="n">
-        <v>22715</v>
+        <v>22672</v>
       </c>
       <c r="M835" s="3" t="inlineStr">
         <is>
@@ -52491,7 +52491,7 @@
         </is>
       </c>
       <c r="E837" s="4" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F837" s="3" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>8023600</v>
       </c>
       <c r="I837" s="5" t="n">
-        <v>22288</v>
+        <v>22350</v>
       </c>
       <c r="J837" s="3" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>8023600</v>
       </c>
       <c r="L837" s="5" t="n">
-        <v>22288</v>
+        <v>22350</v>
       </c>
       <c r="M837" s="3" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         </is>
       </c>
       <c r="E838" s="4" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="F838" s="3" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>40008120</v>
       </c>
       <c r="I838" s="5" t="n">
-        <v>26373</v>
+        <v>26408</v>
       </c>
       <c r="J838" s="3" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>40008120</v>
       </c>
       <c r="L838" s="5" t="n">
-        <v>26373</v>
+        <v>26408</v>
       </c>
       <c r="M838" s="3" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         </is>
       </c>
       <c r="E843" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F843" s="3" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>7007000</v>
       </c>
       <c r="I843" s="5" t="n">
-        <v>25388</v>
+        <v>25480</v>
       </c>
       <c r="J843" s="3" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>7007000</v>
       </c>
       <c r="L843" s="5" t="n">
-        <v>25388</v>
+        <v>25480</v>
       </c>
       <c r="M843" s="3" t="inlineStr">
         <is>
@@ -52925,7 +52925,7 @@
         </is>
       </c>
       <c r="E844" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F844" s="3" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>12880000</v>
       </c>
       <c r="I844" s="5" t="n">
-        <v>30887</v>
+        <v>30962</v>
       </c>
       <c r="J844" s="3" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>12880000</v>
       </c>
       <c r="L844" s="5" t="n">
-        <v>30887</v>
+        <v>30962</v>
       </c>
       <c r="M844" s="3" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         </is>
       </c>
       <c r="E854" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F854" s="3" t="inlineStr">
         <is>
@@ -53569,7 +53569,7 @@
         <v>56800000</v>
       </c>
       <c r="I854" s="5" t="n">
-        <v>37517</v>
+        <v>37541</v>
       </c>
       <c r="J854" s="3" t="inlineStr">
         <is>
@@ -53580,7 +53580,7 @@
         <v>56800000</v>
       </c>
       <c r="L854" s="5" t="n">
-        <v>37517</v>
+        <v>37541</v>
       </c>
       <c r="M854" s="3" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         </is>
       </c>
       <c r="E860" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F860" s="3" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>13102400</v>
       </c>
       <c r="I860" s="5" t="n">
-        <v>31421</v>
+        <v>31496</v>
       </c>
       <c r="J860" s="3" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>13102400</v>
       </c>
       <c r="L860" s="5" t="n">
-        <v>31421</v>
+        <v>31496</v>
       </c>
       <c r="M860" s="3" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         </is>
       </c>
       <c r="E868" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F868" s="3" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>13102400</v>
       </c>
       <c r="I868" s="5" t="n">
-        <v>31421</v>
+        <v>31496</v>
       </c>
       <c r="J868" s="3" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>13102400</v>
       </c>
       <c r="L868" s="5" t="n">
-        <v>31421</v>
+        <v>31496</v>
       </c>
       <c r="M868" s="3" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         </is>
       </c>
       <c r="E875" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F875" s="3" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>6852800</v>
       </c>
       <c r="I875" s="5" t="n">
-        <v>24829</v>
+        <v>24919</v>
       </c>
       <c r="J875" s="3" t="inlineStr">
         <is>
@@ -54882,7 +54882,7 @@
         <v>6852800</v>
       </c>
       <c r="L875" s="5" t="n">
-        <v>24829</v>
+        <v>24919</v>
       </c>
       <c r="M875" s="3" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         </is>
       </c>
       <c r="E876" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F876" s="3" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>13020000</v>
       </c>
       <c r="I876" s="5" t="n">
-        <v>31223</v>
+        <v>31298</v>
       </c>
       <c r="J876" s="3" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>13020000</v>
       </c>
       <c r="L876" s="5" t="n">
-        <v>31223</v>
+        <v>31298</v>
       </c>
       <c r="M876" s="3" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         </is>
       </c>
       <c r="E883" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F883" s="3" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>6774200</v>
       </c>
       <c r="I883" s="5" t="n">
-        <v>24544</v>
+        <v>24633</v>
       </c>
       <c r="J883" s="3" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>6774200</v>
       </c>
       <c r="L883" s="5" t="n">
-        <v>24544</v>
+        <v>24633</v>
       </c>
       <c r="M883" s="3" t="inlineStr">
         <is>
@@ -55413,7 +55413,7 @@
         </is>
       </c>
       <c r="E884" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F884" s="3" t="inlineStr">
         <is>
@@ -55429,7 +55429,7 @@
         <v>14446800</v>
       </c>
       <c r="I884" s="5" t="n">
-        <v>34645</v>
+        <v>34728</v>
       </c>
       <c r="J884" s="3" t="inlineStr">
         <is>
@@ -55440,7 +55440,7 @@
         <v>14446800</v>
       </c>
       <c r="L884" s="5" t="n">
-        <v>34645</v>
+        <v>34728</v>
       </c>
       <c r="M884" s="3" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         </is>
       </c>
       <c r="E892" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F892" s="3" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>13099300</v>
       </c>
       <c r="I892" s="5" t="n">
-        <v>31413</v>
+        <v>31489</v>
       </c>
       <c r="J892" s="3" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>13099300</v>
       </c>
       <c r="L892" s="5" t="n">
-        <v>31413</v>
+        <v>31489</v>
       </c>
       <c r="M892" s="3" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         </is>
       </c>
       <c r="E899" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F899" s="3" t="inlineStr">
         <is>
@@ -56359,7 +56359,7 @@
         <v>6718200</v>
       </c>
       <c r="I899" s="5" t="n">
-        <v>24341</v>
+        <v>24430</v>
       </c>
       <c r="J899" s="3" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>6718200</v>
       </c>
       <c r="L899" s="5" t="n">
-        <v>24341</v>
+        <v>24430</v>
       </c>
       <c r="M899" s="3" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         </is>
       </c>
       <c r="E902" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>43446400</v>
       </c>
       <c r="I902" s="5" t="n">
-        <v>28696</v>
+        <v>28715</v>
       </c>
       <c r="J902" s="3" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>43446400</v>
       </c>
       <c r="L902" s="5" t="n">
-        <v>28696</v>
+        <v>28715</v>
       </c>
       <c r="M902" s="3" t="inlineStr">
         <is>
@@ -56839,7 +56839,7 @@
         </is>
       </c>
       <c r="E907" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F907" s="3" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>6739200</v>
       </c>
       <c r="I907" s="5" t="n">
-        <v>24417</v>
+        <v>24506</v>
       </c>
       <c r="J907" s="3" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>6739200</v>
       </c>
       <c r="L907" s="5" t="n">
-        <v>24417</v>
+        <v>24506</v>
       </c>
       <c r="M907" s="3" t="inlineStr">
         <is>
@@ -56901,7 +56901,7 @@
         </is>
       </c>
       <c r="E908" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F908" s="3" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>12853600</v>
       </c>
       <c r="I908" s="5" t="n">
-        <v>30824</v>
+        <v>30898</v>
       </c>
       <c r="J908" s="3" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>12853600</v>
       </c>
       <c r="L908" s="5" t="n">
-        <v>30824</v>
+        <v>30898</v>
       </c>
       <c r="M908" s="3" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         </is>
       </c>
       <c r="E916" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F916" s="3" t="inlineStr">
         <is>
@@ -57413,7 +57413,7 @@
         <v>13198400</v>
       </c>
       <c r="I916" s="5" t="n">
-        <v>31651</v>
+        <v>31727</v>
       </c>
       <c r="J916" s="3" t="inlineStr">
         <is>
@@ -57424,7 +57424,7 @@
         <v>13198400</v>
       </c>
       <c r="L916" s="5" t="n">
-        <v>31651</v>
+        <v>31727</v>
       </c>
       <c r="M916" s="3" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         </is>
       </c>
       <c r="E918" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F918" s="3" t="inlineStr">
         <is>
@@ -57537,7 +57537,7 @@
         <v>42783300</v>
       </c>
       <c r="I918" s="5" t="n">
-        <v>28258</v>
+        <v>28277</v>
       </c>
       <c r="J918" s="3" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>42783300</v>
       </c>
       <c r="L918" s="5" t="n">
-        <v>28258</v>
+        <v>28277</v>
       </c>
       <c r="M918" s="3" t="inlineStr">
         <is>
@@ -58017,7 +58017,7 @@
         </is>
       </c>
       <c r="E926" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F926" s="3" t="inlineStr">
         <is>
@@ -58033,7 +58033,7 @@
         <v>42929600</v>
       </c>
       <c r="I926" s="5" t="n">
-        <v>28355</v>
+        <v>28374</v>
       </c>
       <c r="J926" s="3" t="inlineStr">
         <is>
@@ -58044,7 +58044,7 @@
         <v>42929600</v>
       </c>
       <c r="L926" s="5" t="n">
-        <v>28355</v>
+        <v>28374</v>
       </c>
       <c r="M926" s="3" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         </is>
       </c>
       <c r="E932" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F932" s="3" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>13113600</v>
       </c>
       <c r="I932" s="5" t="n">
-        <v>31447</v>
+        <v>31523</v>
       </c>
       <c r="J932" s="3" t="inlineStr">
         <is>
@@ -58416,7 +58416,7 @@
         <v>13113600</v>
       </c>
       <c r="L932" s="5" t="n">
-        <v>31447</v>
+        <v>31523</v>
       </c>
       <c r="M932" s="3" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         </is>
       </c>
       <c r="E939" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F939" s="3" t="inlineStr">
         <is>
@@ -58839,7 +58839,7 @@
         <v>6625200</v>
       </c>
       <c r="I939" s="5" t="n">
-        <v>24004</v>
+        <v>24092</v>
       </c>
       <c r="J939" s="3" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>6625200</v>
       </c>
       <c r="L939" s="5" t="n">
-        <v>24004</v>
+        <v>24092</v>
       </c>
       <c r="M939" s="3" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         </is>
       </c>
       <c r="E940" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F940" s="3" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>13346000</v>
       </c>
       <c r="I940" s="5" t="n">
-        <v>32005</v>
+        <v>32082</v>
       </c>
       <c r="J940" s="3" t="inlineStr">
         <is>
@@ -58912,7 +58912,7 @@
         <v>13346000</v>
       </c>
       <c r="L940" s="5" t="n">
-        <v>32005</v>
+        <v>32082</v>
       </c>
       <c r="M940" s="3" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         </is>
       </c>
       <c r="E942" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F942" s="3" t="inlineStr">
         <is>
@@ -59025,7 +59025,7 @@
         <v>41153600</v>
       </c>
       <c r="I942" s="5" t="n">
-        <v>27182</v>
+        <v>27200</v>
       </c>
       <c r="J942" s="3" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>41153600</v>
       </c>
       <c r="L942" s="5" t="n">
-        <v>27182</v>
+        <v>27200</v>
       </c>
       <c r="M942" s="3" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         </is>
       </c>
       <c r="E947" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F947" s="3" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>6565400</v>
       </c>
       <c r="I947" s="5" t="n">
-        <v>23788</v>
+        <v>23874</v>
       </c>
       <c r="J947" s="3" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>6565400</v>
       </c>
       <c r="L947" s="5" t="n">
-        <v>23788</v>
+        <v>23874</v>
       </c>
       <c r="M947" s="3" t="inlineStr">
         <is>
@@ -59381,7 +59381,7 @@
         </is>
       </c>
       <c r="E948" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F948" s="3" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>12630800</v>
       </c>
       <c r="I948" s="5" t="n">
-        <v>30290</v>
+        <v>30362</v>
       </c>
       <c r="J948" s="3" t="inlineStr">
         <is>
@@ -59408,7 +59408,7 @@
         <v>12630800</v>
       </c>
       <c r="L948" s="5" t="n">
-        <v>30290</v>
+        <v>30362</v>
       </c>
       <c r="M948" s="3" t="inlineStr">
         <is>
@@ -59815,7 +59815,7 @@
         </is>
       </c>
       <c r="E955" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F955" s="3" t="inlineStr">
         <is>
@@ -59831,7 +59831,7 @@
         <v>6711100</v>
       </c>
       <c r="I955" s="5" t="n">
-        <v>24316</v>
+        <v>24404</v>
       </c>
       <c r="J955" s="3" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>6711100</v>
       </c>
       <c r="L955" s="5" t="n">
-        <v>24316</v>
+        <v>24404</v>
       </c>
       <c r="M955" s="3" t="inlineStr">
         <is>
@@ -59877,7 +59877,7 @@
         </is>
       </c>
       <c r="E956" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F956" s="3" t="inlineStr">
         <is>
@@ -59893,7 +59893,7 @@
         <v>12624800</v>
       </c>
       <c r="I956" s="5" t="n">
-        <v>30275</v>
+        <v>30348</v>
       </c>
       <c r="J956" s="3" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>12624800</v>
       </c>
       <c r="L956" s="5" t="n">
-        <v>30275</v>
+        <v>30348</v>
       </c>
       <c r="M956" s="3" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         </is>
       </c>
       <c r="E963" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F963" s="3" t="inlineStr">
         <is>
@@ -60327,7 +60327,7 @@
         <v>6526200</v>
       </c>
       <c r="I963" s="5" t="n">
-        <v>23646</v>
+        <v>23732</v>
       </c>
       <c r="J963" s="3" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>6526200</v>
       </c>
       <c r="L963" s="5" t="n">
-        <v>23646</v>
+        <v>23732</v>
       </c>
       <c r="M963" s="3" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         </is>
       </c>
       <c r="E964" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F964" s="3" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>12589600</v>
       </c>
       <c r="I964" s="5" t="n">
-        <v>30191</v>
+        <v>30263</v>
       </c>
       <c r="J964" s="3" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>12589600</v>
       </c>
       <c r="L964" s="5" t="n">
-        <v>30191</v>
+        <v>30263</v>
       </c>
       <c r="M964" s="3" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         </is>
       </c>
       <c r="E966" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F966" s="3" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>41338400</v>
       </c>
       <c r="I966" s="5" t="n">
-        <v>27304</v>
+        <v>27322</v>
       </c>
       <c r="J966" s="3" t="inlineStr">
         <is>
@@ -60524,7 +60524,7 @@
         <v>41338400</v>
       </c>
       <c r="L966" s="5" t="n">
-        <v>27304</v>
+        <v>27322</v>
       </c>
       <c r="M966" s="3" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="E971" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F971" s="3" t="inlineStr">
         <is>
@@ -60823,7 +60823,7 @@
         <v>6588100</v>
       </c>
       <c r="I971" s="5" t="n">
-        <v>23870</v>
+        <v>23957</v>
       </c>
       <c r="J971" s="3" t="inlineStr">
         <is>
@@ -60834,7 +60834,7 @@
         <v>6588100</v>
       </c>
       <c r="L971" s="5" t="n">
-        <v>23870</v>
+        <v>23957</v>
       </c>
       <c r="M971" s="3" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         </is>
       </c>
       <c r="E972" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F972" s="3" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>14352000</v>
       </c>
       <c r="I972" s="5" t="n">
-        <v>34417</v>
+        <v>34500</v>
       </c>
       <c r="J972" s="3" t="inlineStr">
         <is>
@@ -60896,7 +60896,7 @@
         <v>14352000</v>
       </c>
       <c r="L972" s="5" t="n">
-        <v>34417</v>
+        <v>34500</v>
       </c>
       <c r="M972" s="3" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         </is>
       </c>
       <c r="E979" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F979" s="3" t="inlineStr">
         <is>
@@ -61319,7 +61319,7 @@
         <v>6486200</v>
       </c>
       <c r="I979" s="5" t="n">
-        <v>23501</v>
+        <v>23586</v>
       </c>
       <c r="J979" s="3" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>6486200</v>
       </c>
       <c r="L979" s="5" t="n">
-        <v>23501</v>
+        <v>23586</v>
       </c>
       <c r="M979" s="3" t="inlineStr">
         <is>
@@ -61365,7 +61365,7 @@
         </is>
       </c>
       <c r="E980" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F980" s="3" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>12629400</v>
       </c>
       <c r="I980" s="5" t="n">
-        <v>30286</v>
+        <v>30359</v>
       </c>
       <c r="J980" s="3" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>12629400</v>
       </c>
       <c r="L980" s="5" t="n">
-        <v>30286</v>
+        <v>30359</v>
       </c>
       <c r="M980" s="3" t="inlineStr">
         <is>
@@ -61799,7 +61799,7 @@
         </is>
       </c>
       <c r="E987" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F987" s="3" t="inlineStr">
         <is>
@@ -61815,7 +61815,7 @@
         <v>6548400</v>
       </c>
       <c r="I987" s="5" t="n">
-        <v>23726</v>
+        <v>23812</v>
       </c>
       <c r="J987" s="3" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>6548400</v>
       </c>
       <c r="L987" s="5" t="n">
-        <v>23726</v>
+        <v>23812</v>
       </c>
       <c r="M987" s="3" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         </is>
       </c>
       <c r="E988" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F988" s="3" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>12449600</v>
       </c>
       <c r="I988" s="5" t="n">
-        <v>29855</v>
+        <v>29927</v>
       </c>
       <c r="J988" s="3" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>12449600</v>
       </c>
       <c r="L988" s="5" t="n">
-        <v>29855</v>
+        <v>29927</v>
       </c>
       <c r="M988" s="3" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         </is>
       </c>
       <c r="E990" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F990" s="3" t="inlineStr">
         <is>
@@ -62001,7 +62001,7 @@
         <v>42617800</v>
       </c>
       <c r="I990" s="5" t="n">
-        <v>28149</v>
+        <v>28168</v>
       </c>
       <c r="J990" s="3" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>42617800</v>
       </c>
       <c r="L990" s="5" t="n">
-        <v>28149</v>
+        <v>28168</v>
       </c>
       <c r="M990" s="3" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         </is>
       </c>
       <c r="E995" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F995" s="3" t="inlineStr">
         <is>
@@ -62311,7 +62311,7 @@
         <v>6447000</v>
       </c>
       <c r="I995" s="5" t="n">
-        <v>23359</v>
+        <v>23444</v>
       </c>
       <c r="J995" s="3" t="inlineStr">
         <is>
@@ -62322,7 +62322,7 @@
         <v>6447000</v>
       </c>
       <c r="L995" s="5" t="n">
-        <v>23359</v>
+        <v>23444</v>
       </c>
       <c r="M995" s="3" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         </is>
       </c>
       <c r="E996" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F996" s="3" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>12397600</v>
       </c>
       <c r="I996" s="5" t="n">
-        <v>29730</v>
+        <v>29802</v>
       </c>
       <c r="J996" s="3" t="inlineStr">
         <is>
@@ -62384,7 +62384,7 @@
         <v>12397600</v>
       </c>
       <c r="L996" s="5" t="n">
-        <v>29730</v>
+        <v>29802</v>
       </c>
       <c r="M996" s="3" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         </is>
       </c>
       <c r="E998" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F998" s="3" t="inlineStr">
         <is>
@@ -62497,7 +62497,7 @@
         <v>40548000</v>
       </c>
       <c r="I998" s="5" t="n">
-        <v>26782</v>
+        <v>26800</v>
       </c>
       <c r="J998" s="3" t="inlineStr">
         <is>
@@ -62508,7 +62508,7 @@
         <v>40548000</v>
       </c>
       <c r="L998" s="5" t="n">
-        <v>26782</v>
+        <v>26800</v>
       </c>
       <c r="M998" s="3" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         </is>
       </c>
       <c r="E1003" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1003" s="3" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>6428600</v>
       </c>
       <c r="I1003" s="5" t="n">
-        <v>23292</v>
+        <v>23377</v>
       </c>
       <c r="J1003" s="3" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>6428600</v>
       </c>
       <c r="L1003" s="5" t="n">
-        <v>23292</v>
+        <v>23377</v>
       </c>
       <c r="M1003" s="3" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         </is>
       </c>
       <c r="E1004" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1004" s="3" t="inlineStr">
         <is>
@@ -62869,7 +62869,7 @@
         <v>12345600</v>
       </c>
       <c r="I1004" s="5" t="n">
-        <v>29606</v>
+        <v>29677</v>
       </c>
       <c r="J1004" s="3" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>12345600</v>
       </c>
       <c r="L1004" s="5" t="n">
-        <v>29606</v>
+        <v>29677</v>
       </c>
       <c r="M1004" s="3" t="inlineStr">
         <is>
@@ -63287,7 +63287,7 @@
         </is>
       </c>
       <c r="E1011" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1011" s="3" t="inlineStr">
         <is>
@@ -63303,7 +63303,7 @@
         <v>6428600</v>
       </c>
       <c r="I1011" s="5" t="n">
-        <v>23292</v>
+        <v>23377</v>
       </c>
       <c r="J1011" s="3" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>6428600</v>
       </c>
       <c r="L1011" s="5" t="n">
-        <v>23292</v>
+        <v>23377</v>
       </c>
       <c r="M1011" s="3" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         </is>
       </c>
       <c r="E1014" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1014" s="3" t="inlineStr">
         <is>
@@ -63489,7 +63489,7 @@
         <v>40335200</v>
       </c>
       <c r="I1014" s="5" t="n">
-        <v>26641</v>
+        <v>26659</v>
       </c>
       <c r="J1014" s="3" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>40335200</v>
       </c>
       <c r="L1014" s="5" t="n">
-        <v>26641</v>
+        <v>26659</v>
       </c>
       <c r="M1014" s="3" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         </is>
       </c>
       <c r="E1020" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1020" s="3" t="inlineStr">
         <is>
@@ -63861,7 +63861,7 @@
         <v>12374300</v>
       </c>
       <c r="I1020" s="5" t="n">
-        <v>29675</v>
+        <v>29746</v>
       </c>
       <c r="J1020" s="3" t="inlineStr">
         <is>
@@ -63872,7 +63872,7 @@
         <v>12374300</v>
       </c>
       <c r="L1020" s="5" t="n">
-        <v>29675</v>
+        <v>29746</v>
       </c>
       <c r="M1020" s="3" t="inlineStr">
         <is>
@@ -64279,7 +64279,7 @@
         </is>
       </c>
       <c r="E1027" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1027" s="3" t="inlineStr">
         <is>
@@ -64295,7 +64295,7 @@
         <v>6331000</v>
       </c>
       <c r="I1027" s="5" t="n">
-        <v>22938</v>
+        <v>23022</v>
       </c>
       <c r="J1027" s="3" t="inlineStr">
         <is>
@@ -64306,7 +64306,7 @@
         <v>6331000</v>
       </c>
       <c r="L1027" s="5" t="n">
-        <v>22938</v>
+        <v>23022</v>
       </c>
       <c r="M1027" s="3" t="inlineStr">
         <is>
@@ -64341,7 +64341,7 @@
         </is>
       </c>
       <c r="E1028" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1028" s="3" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>12312800</v>
       </c>
       <c r="I1028" s="5" t="n">
-        <v>29527</v>
+        <v>29598</v>
       </c>
       <c r="J1028" s="3" t="inlineStr">
         <is>
@@ -64368,7 +64368,7 @@
         <v>12312800</v>
       </c>
       <c r="L1028" s="5" t="n">
-        <v>29527</v>
+        <v>29598</v>
       </c>
       <c r="M1028" s="3" t="inlineStr">
         <is>
@@ -64465,7 +64465,7 @@
         </is>
       </c>
       <c r="E1030" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1030" s="3" t="inlineStr">
         <is>
@@ -64481,7 +64481,7 @@
         <v>41760000</v>
       </c>
       <c r="I1030" s="5" t="n">
-        <v>27583</v>
+        <v>27601</v>
       </c>
       <c r="J1030" s="3" t="inlineStr">
         <is>
@@ -64492,7 +64492,7 @@
         <v>41760000</v>
       </c>
       <c r="L1030" s="5" t="n">
-        <v>27583</v>
+        <v>27601</v>
       </c>
       <c r="M1030" s="3" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         </is>
       </c>
       <c r="E1035" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1035" s="3" t="inlineStr">
         <is>
@@ -64791,7 +64791,7 @@
         <v>6457700</v>
       </c>
       <c r="I1035" s="5" t="n">
-        <v>23397</v>
+        <v>23483</v>
       </c>
       <c r="J1035" s="3" t="inlineStr">
         <is>
@@ -64802,7 +64802,7 @@
         <v>6457700</v>
       </c>
       <c r="L1035" s="5" t="n">
-        <v>23397</v>
+        <v>23483</v>
       </c>
       <c r="M1035" s="3" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         </is>
       </c>
       <c r="E1036" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1036" s="3" t="inlineStr">
         <is>
@@ -64853,7 +64853,7 @@
         <v>12026000</v>
       </c>
       <c r="I1036" s="5" t="n">
-        <v>28839</v>
+        <v>28909</v>
       </c>
       <c r="J1036" s="3" t="inlineStr">
         <is>
@@ -64864,7 +64864,7 @@
         <v>12026000</v>
       </c>
       <c r="L1036" s="5" t="n">
-        <v>28839</v>
+        <v>28909</v>
       </c>
       <c r="M1036" s="3" t="inlineStr">
         <is>
@@ -65271,7 +65271,7 @@
         </is>
       </c>
       <c r="E1043" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1043" s="3" t="inlineStr">
         <is>
@@ -65287,7 +65287,7 @@
         <v>6424900</v>
       </c>
       <c r="I1043" s="5" t="n">
-        <v>23279</v>
+        <v>23363</v>
       </c>
       <c r="J1043" s="3" t="inlineStr">
         <is>
@@ -65298,7 +65298,7 @@
         <v>6424900</v>
       </c>
       <c r="L1043" s="5" t="n">
-        <v>23279</v>
+        <v>23363</v>
       </c>
       <c r="M1043" s="3" t="inlineStr">
         <is>
@@ -65333,7 +65333,7 @@
         </is>
       </c>
       <c r="E1044" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1044" s="3" t="inlineStr">
         <is>
@@ -65349,7 +65349,7 @@
         <v>12100500</v>
       </c>
       <c r="I1044" s="5" t="n">
-        <v>29018</v>
+        <v>29088</v>
       </c>
       <c r="J1044" s="3" t="inlineStr">
         <is>
@@ -65360,7 +65360,7 @@
         <v>12100500</v>
       </c>
       <c r="L1044" s="5" t="n">
-        <v>29018</v>
+        <v>29088</v>
       </c>
       <c r="M1044" s="3" t="inlineStr">
         <is>
@@ -65457,7 +65457,7 @@
         </is>
       </c>
       <c r="E1046" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1046" s="3" t="inlineStr">
         <is>
@@ -65473,7 +65473,7 @@
         <v>39218400</v>
       </c>
       <c r="I1046" s="5" t="n">
-        <v>25904</v>
+        <v>25921</v>
       </c>
       <c r="J1046" s="3" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>39218400</v>
       </c>
       <c r="L1046" s="5" t="n">
-        <v>25904</v>
+        <v>25921</v>
       </c>
       <c r="M1046" s="3" t="inlineStr">
         <is>
@@ -65767,7 +65767,7 @@
         </is>
       </c>
       <c r="E1051" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1051" s="3" t="inlineStr">
         <is>
@@ -65783,7 +65783,7 @@
         <v>6286400</v>
       </c>
       <c r="I1051" s="5" t="n">
-        <v>22777</v>
+        <v>22860</v>
       </c>
       <c r="J1051" s="3" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>6286400</v>
       </c>
       <c r="L1051" s="5" t="n">
-        <v>22777</v>
+        <v>22860</v>
       </c>
       <c r="M1051" s="3" t="inlineStr">
         <is>
@@ -65829,7 +65829,7 @@
         </is>
       </c>
       <c r="E1052" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1052" s="3" t="inlineStr">
         <is>
@@ -65845,7 +65845,7 @@
         <v>12025600</v>
       </c>
       <c r="I1052" s="5" t="n">
-        <v>28838</v>
+        <v>28908</v>
       </c>
       <c r="J1052" s="3" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         <v>12025600</v>
       </c>
       <c r="L1052" s="5" t="n">
-        <v>28838</v>
+        <v>28908</v>
       </c>
       <c r="M1052" s="3" t="inlineStr">
         <is>
@@ -65953,7 +65953,7 @@
         </is>
       </c>
       <c r="E1054" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1054" s="3" t="inlineStr">
         <is>
@@ -65969,7 +65969,7 @@
         <v>39743200</v>
       </c>
       <c r="I1054" s="5" t="n">
-        <v>26250</v>
+        <v>26268</v>
       </c>
       <c r="J1054" s="3" t="inlineStr">
         <is>
@@ -65980,7 +65980,7 @@
         <v>39743200</v>
       </c>
       <c r="L1054" s="5" t="n">
-        <v>26250</v>
+        <v>26268</v>
       </c>
       <c r="M1054" s="3" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         </is>
       </c>
       <c r="E1059" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1059" s="3" t="inlineStr">
         <is>
@@ -66279,7 +66279,7 @@
         <v>6174600</v>
       </c>
       <c r="I1059" s="5" t="n">
-        <v>22372</v>
+        <v>22453</v>
       </c>
       <c r="J1059" s="3" t="inlineStr">
         <is>
@@ -66290,7 +66290,7 @@
         <v>6174600</v>
       </c>
       <c r="L1059" s="5" t="n">
-        <v>22372</v>
+        <v>22453</v>
       </c>
       <c r="M1059" s="3" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         </is>
       </c>
       <c r="E1060" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1060" s="3" t="inlineStr">
         <is>
@@ -66341,7 +66341,7 @@
         <v>12010000</v>
       </c>
       <c r="I1060" s="5" t="n">
-        <v>28801</v>
+        <v>28870</v>
       </c>
       <c r="J1060" s="3" t="inlineStr">
         <is>
@@ -66352,7 +66352,7 @@
         <v>12010000</v>
       </c>
       <c r="L1060" s="5" t="n">
-        <v>28801</v>
+        <v>28870</v>
       </c>
       <c r="M1060" s="3" t="inlineStr">
         <is>
@@ -66449,7 +66449,7 @@
         </is>
       </c>
       <c r="E1062" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1062" s="3" t="inlineStr">
         <is>
@@ -66465,7 +66465,7 @@
         <v>38708800</v>
       </c>
       <c r="I1062" s="5" t="n">
-        <v>25567</v>
+        <v>25584</v>
       </c>
       <c r="J1062" s="3" t="inlineStr">
         <is>
@@ -66476,7 +66476,7 @@
         <v>38708800</v>
       </c>
       <c r="L1062" s="5" t="n">
-        <v>25567</v>
+        <v>25584</v>
       </c>
       <c r="M1062" s="3" t="inlineStr">
         <is>
@@ -66759,7 +66759,7 @@
         </is>
       </c>
       <c r="E1067" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1067" s="3" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>6328900</v>
       </c>
       <c r="I1067" s="5" t="n">
-        <v>22931</v>
+        <v>23014</v>
       </c>
       <c r="J1067" s="3" t="inlineStr">
         <is>
@@ -66786,7 +66786,7 @@
         <v>6328900</v>
       </c>
       <c r="L1067" s="5" t="n">
-        <v>22931</v>
+        <v>23014</v>
       </c>
       <c r="M1067" s="3" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         </is>
       </c>
       <c r="E1068" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1068" s="3" t="inlineStr">
         <is>
@@ -66837,7 +66837,7 @@
         <v>11605600</v>
       </c>
       <c r="I1068" s="5" t="n">
-        <v>27831</v>
+        <v>27898</v>
       </c>
       <c r="J1068" s="3" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>11605600</v>
       </c>
       <c r="L1068" s="5" t="n">
-        <v>27831</v>
+        <v>27898</v>
       </c>
       <c r="M1068" s="3" t="inlineStr">
         <is>
@@ -67255,7 +67255,7 @@
         </is>
       </c>
       <c r="E1075" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1075" s="3" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>6221100</v>
       </c>
       <c r="I1075" s="5" t="n">
-        <v>22540</v>
+        <v>22622</v>
       </c>
       <c r="J1075" s="3" t="inlineStr">
         <is>
@@ -67282,7 +67282,7 @@
         <v>6221100</v>
       </c>
       <c r="L1075" s="5" t="n">
-        <v>22540</v>
+        <v>22622</v>
       </c>
       <c r="M1075" s="3" t="inlineStr">
         <is>
@@ -67317,7 +67317,7 @@
         </is>
       </c>
       <c r="E1076" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1076" s="3" t="inlineStr">
         <is>
@@ -67333,7 +67333,7 @@
         <v>11605600</v>
       </c>
       <c r="I1076" s="5" t="n">
-        <v>27831</v>
+        <v>27898</v>
       </c>
       <c r="J1076" s="3" t="inlineStr">
         <is>
@@ -67344,7 +67344,7 @@
         <v>11605600</v>
       </c>
       <c r="L1076" s="5" t="n">
-        <v>27831</v>
+        <v>27898</v>
       </c>
       <c r="M1076" s="3" t="inlineStr">
         <is>
@@ -67441,7 +67441,7 @@
         </is>
       </c>
       <c r="E1078" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1078" s="3" t="inlineStr">
         <is>
@@ -67457,7 +67457,7 @@
         <v>39665700</v>
       </c>
       <c r="I1078" s="5" t="n">
-        <v>26199</v>
+        <v>26217</v>
       </c>
       <c r="J1078" s="3" t="inlineStr">
         <is>
@@ -67468,7 +67468,7 @@
         <v>39665700</v>
       </c>
       <c r="L1078" s="5" t="n">
-        <v>26199</v>
+        <v>26217</v>
       </c>
       <c r="M1078" s="3" t="inlineStr">
         <is>
@@ -67751,7 +67751,7 @@
         </is>
       </c>
       <c r="E1083" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1083" s="3" t="inlineStr">
         <is>
@@ -67767,7 +67767,7 @@
         <v>6142200</v>
       </c>
       <c r="I1083" s="5" t="n">
-        <v>22254</v>
+        <v>22335</v>
       </c>
       <c r="J1083" s="3" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>6142200</v>
       </c>
       <c r="L1083" s="5" t="n">
-        <v>22254</v>
+        <v>22335</v>
       </c>
       <c r="M1083" s="3" t="inlineStr">
         <is>
@@ -67813,7 +67813,7 @@
         </is>
       </c>
       <c r="E1084" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1084" s="3" t="inlineStr">
         <is>
@@ -67829,7 +67829,7 @@
         <v>12077600</v>
       </c>
       <c r="I1084" s="5" t="n">
-        <v>28963</v>
+        <v>29033</v>
       </c>
       <c r="J1084" s="3" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         <v>12077600</v>
       </c>
       <c r="L1084" s="5" t="n">
-        <v>28963</v>
+        <v>29033</v>
       </c>
       <c r="M1084" s="3" t="inlineStr">
         <is>
@@ -67937,7 +67937,7 @@
         </is>
       </c>
       <c r="E1086" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1086" s="3" t="inlineStr">
         <is>
@@ -67953,7 +67953,7 @@
         <v>38564800</v>
       </c>
       <c r="I1086" s="5" t="n">
-        <v>25472</v>
+        <v>25489</v>
       </c>
       <c r="J1086" s="3" t="inlineStr">
         <is>
@@ -67964,7 +67964,7 @@
         <v>38564800</v>
       </c>
       <c r="L1086" s="5" t="n">
-        <v>25472</v>
+        <v>25489</v>
       </c>
       <c r="M1086" s="3" t="inlineStr">
         <is>
@@ -68247,7 +68247,7 @@
         </is>
       </c>
       <c r="E1091" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1091" s="3" t="inlineStr">
         <is>
@@ -68263,7 +68263,7 @@
         <v>6291200</v>
       </c>
       <c r="I1091" s="5" t="n">
-        <v>22794</v>
+        <v>22877</v>
       </c>
       <c r="J1091" s="3" t="inlineStr">
         <is>
@@ -68274,7 +68274,7 @@
         <v>6291200</v>
       </c>
       <c r="L1091" s="5" t="n">
-        <v>22794</v>
+        <v>22877</v>
       </c>
       <c r="M1091" s="3" t="inlineStr">
         <is>
@@ -68743,7 +68743,7 @@
         </is>
       </c>
       <c r="E1099" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1099" s="3" t="inlineStr">
         <is>
@@ -68759,7 +68759,7 @@
         <v>6100200</v>
       </c>
       <c r="I1099" s="5" t="n">
-        <v>22102</v>
+        <v>22183</v>
       </c>
       <c r="J1099" s="3" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         <v>6100200</v>
       </c>
       <c r="L1099" s="5" t="n">
-        <v>22102</v>
+        <v>22183</v>
       </c>
       <c r="M1099" s="3" t="inlineStr">
         <is>
@@ -68805,7 +68805,7 @@
         </is>
       </c>
       <c r="E1100" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1100" s="3" t="inlineStr">
         <is>
@@ -68821,7 +68821,7 @@
         <v>11792000</v>
       </c>
       <c r="I1100" s="5" t="n">
-        <v>28278</v>
+        <v>28346</v>
       </c>
       <c r="J1100" s="3" t="inlineStr">
         <is>
@@ -68832,7 +68832,7 @@
         <v>11792000</v>
       </c>
       <c r="L1100" s="5" t="n">
-        <v>28278</v>
+        <v>28346</v>
       </c>
       <c r="M1100" s="3" t="inlineStr">
         <is>
@@ -69239,7 +69239,7 @@
         </is>
       </c>
       <c r="E1107" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1107" s="3" t="inlineStr">
         <is>
@@ -69255,7 +69255,7 @@
         <v>6123000</v>
       </c>
       <c r="I1107" s="5" t="n">
-        <v>22185</v>
+        <v>22265</v>
       </c>
       <c r="J1107" s="3" t="inlineStr">
         <is>
@@ -69266,7 +69266,7 @@
         <v>6123000</v>
       </c>
       <c r="L1107" s="5" t="n">
-        <v>22185</v>
+        <v>22265</v>
       </c>
       <c r="M1107" s="3" t="inlineStr">
         <is>
@@ -69301,7 +69301,7 @@
         </is>
       </c>
       <c r="E1108" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1108" s="3" t="inlineStr">
         <is>
@@ -69317,7 +69317,7 @@
         <v>10894800</v>
       </c>
       <c r="I1108" s="5" t="n">
-        <v>26127</v>
+        <v>26189</v>
       </c>
       <c r="J1108" s="3" t="inlineStr">
         <is>
@@ -69328,7 +69328,7 @@
         <v>10894800</v>
       </c>
       <c r="L1108" s="5" t="n">
-        <v>26127</v>
+        <v>26189</v>
       </c>
       <c r="M1108" s="3" t="inlineStr">
         <is>
@@ -69425,7 +69425,7 @@
         </is>
       </c>
       <c r="E1110" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1110" s="3" t="inlineStr">
         <is>
@@ -69441,7 +69441,7 @@
         <v>37300000</v>
       </c>
       <c r="I1110" s="5" t="n">
-        <v>24637</v>
+        <v>24653</v>
       </c>
       <c r="J1110" s="3" t="inlineStr">
         <is>
@@ -69452,7 +69452,7 @@
         <v>37300000</v>
       </c>
       <c r="L1110" s="5" t="n">
-        <v>24637</v>
+        <v>24653</v>
       </c>
       <c r="M1110" s="3" t="inlineStr">
         <is>
@@ -69735,7 +69735,7 @@
         </is>
       </c>
       <c r="E1115" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1115" s="3" t="inlineStr">
         <is>
@@ -69751,7 +69751,7 @@
         <v>6117400</v>
       </c>
       <c r="I1115" s="5" t="n">
-        <v>22164</v>
+        <v>22245</v>
       </c>
       <c r="J1115" s="3" t="inlineStr">
         <is>
@@ -69762,7 +69762,7 @@
         <v>6117400</v>
       </c>
       <c r="L1115" s="5" t="n">
-        <v>22164</v>
+        <v>22245</v>
       </c>
       <c r="M1115" s="3" t="inlineStr">
         <is>
@@ -69921,7 +69921,7 @@
         </is>
       </c>
       <c r="E1118" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1118" s="3" t="inlineStr">
         <is>
@@ -69937,7 +69937,7 @@
         <v>36642400</v>
       </c>
       <c r="I1118" s="5" t="n">
-        <v>24202</v>
+        <v>24218</v>
       </c>
       <c r="J1118" s="3" t="inlineStr">
         <is>
@@ -69948,7 +69948,7 @@
         <v>36642400</v>
       </c>
       <c r="L1118" s="5" t="n">
-        <v>24202</v>
+        <v>24218</v>
       </c>
       <c r="M1118" s="3" t="inlineStr">
         <is>
@@ -70231,7 +70231,7 @@
         </is>
       </c>
       <c r="E1123" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1123" s="3" t="inlineStr">
         <is>
@@ -70247,7 +70247,7 @@
         <v>6111000</v>
       </c>
       <c r="I1123" s="5" t="n">
-        <v>22141</v>
+        <v>22222</v>
       </c>
       <c r="J1123" s="3" t="inlineStr">
         <is>
@@ -70258,7 +70258,7 @@
         <v>6111000</v>
       </c>
       <c r="L1123" s="5" t="n">
-        <v>22141</v>
+        <v>22222</v>
       </c>
       <c r="M1123" s="3" t="inlineStr">
         <is>
@@ -70293,7 +70293,7 @@
         </is>
       </c>
       <c r="E1124" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1124" s="3" t="inlineStr">
         <is>
@@ -70309,7 +70309,7 @@
         <v>10768900</v>
       </c>
       <c r="I1124" s="5" t="n">
-        <v>25825</v>
+        <v>25887</v>
       </c>
       <c r="J1124" s="3" t="inlineStr">
         <is>
@@ -70320,7 +70320,7 @@
         <v>10768900</v>
       </c>
       <c r="L1124" s="5" t="n">
-        <v>25825</v>
+        <v>25887</v>
       </c>
       <c r="M1124" s="3" t="inlineStr">
         <is>
@@ -70727,7 +70727,7 @@
         </is>
       </c>
       <c r="E1131" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1131" s="3" t="inlineStr">
         <is>
@@ -70743,7 +70743,7 @@
         <v>6105400</v>
       </c>
       <c r="I1131" s="5" t="n">
-        <v>22121</v>
+        <v>22201</v>
       </c>
       <c r="J1131" s="3" t="inlineStr">
         <is>
@@ -70754,7 +70754,7 @@
         <v>6105400</v>
       </c>
       <c r="L1131" s="5" t="n">
-        <v>22121</v>
+        <v>22201</v>
       </c>
       <c r="M1131" s="3" t="inlineStr">
         <is>
@@ -70789,7 +70789,7 @@
         </is>
       </c>
       <c r="E1132" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1132" s="3" t="inlineStr">
         <is>
@@ -70805,7 +70805,7 @@
         <v>11236800</v>
       </c>
       <c r="I1132" s="5" t="n">
-        <v>26947</v>
+        <v>27012</v>
       </c>
       <c r="J1132" s="3" t="inlineStr">
         <is>
@@ -70816,7 +70816,7 @@
         <v>11236800</v>
       </c>
       <c r="L1132" s="5" t="n">
-        <v>26947</v>
+        <v>27012</v>
       </c>
       <c r="M1132" s="3" t="inlineStr">
         <is>
@@ -71223,7 +71223,7 @@
         </is>
       </c>
       <c r="E1139" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1139" s="3" t="inlineStr">
         <is>
@@ -71239,7 +71239,7 @@
         <v>6099000</v>
       </c>
       <c r="I1139" s="5" t="n">
-        <v>22098</v>
+        <v>22178</v>
       </c>
       <c r="J1139" s="3" t="inlineStr">
         <is>
@@ -71250,7 +71250,7 @@
         <v>6099000</v>
       </c>
       <c r="L1139" s="5" t="n">
-        <v>22098</v>
+        <v>22178</v>
       </c>
       <c r="M1139" s="3" t="inlineStr">
         <is>
@@ -71285,7 +71285,7 @@
         </is>
       </c>
       <c r="E1140" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1140" s="3" t="inlineStr">
         <is>
@@ -71301,7 +71301,7 @@
         <v>10669300</v>
       </c>
       <c r="I1140" s="5" t="n">
-        <v>25586</v>
+        <v>25647</v>
       </c>
       <c r="J1140" s="3" t="inlineStr">
         <is>
@@ -71312,7 +71312,7 @@
         <v>10669300</v>
       </c>
       <c r="L1140" s="5" t="n">
-        <v>25586</v>
+        <v>25647</v>
       </c>
       <c r="M1140" s="3" t="inlineStr">
         <is>
@@ -71719,7 +71719,7 @@
         </is>
       </c>
       <c r="E1147" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1147" s="3" t="inlineStr">
         <is>
@@ -71735,7 +71735,7 @@
         <v>6093400</v>
       </c>
       <c r="I1147" s="5" t="n">
-        <v>22078</v>
+        <v>22158</v>
       </c>
       <c r="J1147" s="3" t="inlineStr">
         <is>
@@ -71746,7 +71746,7 @@
         <v>6093400</v>
       </c>
       <c r="L1147" s="5" t="n">
-        <v>22078</v>
+        <v>22158</v>
       </c>
       <c r="M1147" s="3" t="inlineStr">
         <is>
@@ -71781,7 +71781,7 @@
         </is>
       </c>
       <c r="E1148" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1148" s="3" t="inlineStr">
         <is>
@@ -71797,7 +71797,7 @@
         <v>10698400</v>
       </c>
       <c r="I1148" s="5" t="n">
-        <v>25656</v>
+        <v>25717</v>
       </c>
       <c r="J1148" s="3" t="inlineStr">
         <is>
@@ -71808,7 +71808,7 @@
         <v>10698400</v>
       </c>
       <c r="L1148" s="5" t="n">
-        <v>25656</v>
+        <v>25717</v>
       </c>
       <c r="M1148" s="3" t="inlineStr">
         <is>
@@ -71905,7 +71905,7 @@
         </is>
       </c>
       <c r="E1150" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1150" s="3" t="inlineStr">
         <is>
@@ -71921,7 +71921,7 @@
         <v>37825000</v>
       </c>
       <c r="I1150" s="5" t="n">
-        <v>24983</v>
+        <v>25000</v>
       </c>
       <c r="J1150" s="3" t="inlineStr">
         <is>
@@ -71932,7 +71932,7 @@
         <v>37825000</v>
       </c>
       <c r="L1150" s="5" t="n">
-        <v>24983</v>
+        <v>25000</v>
       </c>
       <c r="M1150" s="3" t="inlineStr">
         <is>
@@ -72215,7 +72215,7 @@
         </is>
       </c>
       <c r="E1155" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F1155" s="3" t="inlineStr">
         <is>
@@ -72231,7 +72231,7 @@
         <v>6136000</v>
       </c>
       <c r="I1155" s="5" t="n">
-        <v>22232</v>
+        <v>22313</v>
       </c>
       <c r="J1155" s="3" t="inlineStr">
         <is>
@@ -72242,7 +72242,7 @@
         <v>6136000</v>
       </c>
       <c r="L1155" s="5" t="n">
-        <v>22232</v>
+        <v>22313</v>
       </c>
       <c r="M1155" s="3" t="inlineStr">
         <is>
@@ -72277,7 +72277,7 @@
         </is>
       </c>
       <c r="E1156" s="4" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1156" s="3" t="inlineStr">
         <is>
@@ -72293,7 +72293,7 @@
         <v>10514300</v>
       </c>
       <c r="I1156" s="5" t="n">
-        <v>25214</v>
+        <v>25275</v>
       </c>
       <c r="J1156" s="3" t="inlineStr">
         <is>
@@ -72304,7 +72304,7 @@
         <v>10514300</v>
       </c>
       <c r="L1156" s="5" t="n">
-        <v>25214</v>
+        <v>25275</v>
       </c>
       <c r="M1156" s="3" t="inlineStr">
         <is>
@@ -72401,7 +72401,7 @@
         </is>
       </c>
       <c r="E1158" s="4" t="n">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F1158" s="3" t="inlineStr">
         <is>
@@ -72417,7 +72417,7 @@
         <v>34315200</v>
       </c>
       <c r="I1158" s="5" t="n">
-        <v>22665</v>
+        <v>22680</v>
       </c>
       <c r="J1158" s="3" t="inlineStr">
         <is>
@@ -72428,7 +72428,7 @@
         <v>34315200</v>
       </c>
       <c r="L1158" s="5" t="n">
-        <v>22665</v>
+        <v>22680</v>
       </c>
       <c r="M1158" s="3" t="inlineStr">
         <is>
@@ -72673,7 +72673,7 @@
         </is>
       </c>
       <c r="E1162" s="4" t="n">
-        <v>1573</v>
+        <v>1629</v>
       </c>
       <c r="F1162" s="3" t="inlineStr">
         <is>
@@ -72689,7 +72689,7 @@
         <v>48055500</v>
       </c>
       <c r="I1162" s="5" t="n">
-        <v>30550</v>
+        <v>29500</v>
       </c>
       <c r="J1162" s="3" t="inlineStr">
         <is>
@@ -72700,7 +72700,7 @@
         <v>48055500</v>
       </c>
       <c r="L1162" s="5" t="n">
-        <v>30550</v>
+        <v>29500</v>
       </c>
       <c r="M1162" s="3" t="inlineStr">
         <is>
@@ -72945,7 +72945,7 @@
         </is>
       </c>
       <c r="E1166" s="4" t="n">
-        <v>1573</v>
+        <v>1629</v>
       </c>
       <c r="F1166" s="3" t="inlineStr">
         <is>
@@ -72961,7 +72961,7 @@
         <v>47078100</v>
       </c>
       <c r="I1166" s="5" t="n">
-        <v>29929</v>
+        <v>28900</v>
       </c>
       <c r="J1166" s="3" t="inlineStr">
         <is>
@@ -72972,7 +72972,7 @@
         <v>47078100</v>
       </c>
       <c r="L1166" s="5" t="n">
-        <v>29929</v>
+        <v>28900</v>
       </c>
       <c r="M1166" s="3" t="inlineStr">
         <is>
@@ -73007,7 +73007,7 @@
         </is>
       </c>
       <c r="E1167" s="4" t="n">
-        <v>1584</v>
+        <v>1640</v>
       </c>
       <c r="F1167" s="3" t="inlineStr">
         <is>
@@ -73023,7 +73023,7 @@
         <v>45920000</v>
       </c>
       <c r="I1167" s="5" t="n">
-        <v>28990</v>
+        <v>28000</v>
       </c>
       <c r="J1167" s="3" t="inlineStr">
         <is>
@@ -73034,7 +73034,7 @@
         <v>45920000</v>
       </c>
       <c r="L1167" s="5" t="n">
-        <v>28990</v>
+        <v>28000</v>
       </c>
       <c r="M1167" s="3" t="inlineStr">
         <is>
@@ -73069,7 +73069,7 @@
         </is>
       </c>
       <c r="E1168" s="4" t="n">
-        <v>2112</v>
+        <v>2171</v>
       </c>
       <c r="F1168" s="3" t="inlineStr">
         <is>
@@ -73085,7 +73085,7 @@
         <v>61439300</v>
       </c>
       <c r="I1168" s="5" t="n">
-        <v>29091</v>
+        <v>28300</v>
       </c>
       <c r="J1168" s="3" t="inlineStr">
         <is>
@@ -73096,7 +73096,7 @@
         <v>61439300</v>
       </c>
       <c r="L1168" s="5" t="n">
-        <v>29091</v>
+        <v>28300</v>
       </c>
       <c r="M1168" s="3" t="inlineStr">
         <is>
@@ -73131,7 +73131,7 @@
         </is>
       </c>
       <c r="E1169" s="4" t="n">
-        <v>1584</v>
+        <v>1640</v>
       </c>
       <c r="F1169" s="3" t="inlineStr">
         <is>
@@ -73147,7 +73147,7 @@
         <v>48749000</v>
       </c>
       <c r="I1169" s="5" t="n">
-        <v>30776</v>
+        <v>29725</v>
       </c>
       <c r="J1169" s="3" t="inlineStr">
         <is>
@@ -73158,7 +73158,7 @@
         <v>48749000</v>
       </c>
       <c r="L1169" s="5" t="n">
-        <v>30776</v>
+        <v>29725</v>
       </c>
       <c r="M1169" s="3" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         </is>
       </c>
       <c r="E1170" s="4" t="n">
-        <v>2112</v>
+        <v>2171</v>
       </c>
       <c r="F1170" s="3" t="inlineStr">
         <is>
@@ -73209,7 +73209,7 @@
         <v>54275000</v>
       </c>
       <c r="I1170" s="5" t="n">
-        <v>25698</v>
+        <v>25000</v>
       </c>
       <c r="J1170" s="3" t="inlineStr">
         <is>
@@ -73220,7 +73220,7 @@
         <v>54275000</v>
       </c>
       <c r="L1170" s="5" t="n">
-        <v>25698</v>
+        <v>25000</v>
       </c>
       <c r="M1170" s="3" t="inlineStr">
         <is>
@@ -73465,7 +73465,7 @@
         </is>
       </c>
       <c r="E1174" s="4" t="n">
-        <v>2112</v>
+        <v>2171</v>
       </c>
       <c r="F1174" s="3" t="inlineStr">
         <is>
@@ -73481,7 +73481,7 @@
         <v>64700000</v>
       </c>
       <c r="I1174" s="5" t="n">
-        <v>30634</v>
+        <v>29802</v>
       </c>
       <c r="J1174" s="3" t="inlineStr">
         <is>
@@ -73492,7 +73492,7 @@
         <v>64700000</v>
       </c>
       <c r="L1174" s="5" t="n">
-        <v>30634</v>
+        <v>29802</v>
       </c>
       <c r="M1174" s="3" t="inlineStr">
         <is>
@@ -73722,9 +73722,9 @@
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $960万
-$25,335/呎
+$25,402/呎
 (19年-11月-20日)</t>
         </is>
       </c>
@@ -73801,9 +73801,9 @@
       </c>
       <c r="I6" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $930万
-$24,536/呎
+$24,601/呎
 (19年-11月-06日)</t>
         </is>
       </c>
@@ -73880,9 +73880,9 @@
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $946万
-$24,972/呎
+$25,038/呎
 (19年-10月-23日)</t>
         </is>
       </c>
@@ -74038,9 +74038,9 @@
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $911万
-$24,040/呎
+$24,103/呎
 (19年-11月-06日)</t>
         </is>
       </c>
@@ -74117,9 +74117,9 @@
       </c>
       <c r="I10" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $903万
-$23,815/呎
+$23,878/呎
 (19年-11月-05日)</t>
         </is>
       </c>
@@ -74196,9 +74196,9 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $900万
-$23,753/呎
+$23,815/呎
 (19年-11月-05日)</t>
         </is>
       </c>
@@ -74275,9 +74275,9 @@
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $923万
-$24,351/呎
+$24,415/呎
 (19年-11月-07日)</t>
         </is>
       </c>
@@ -74354,9 +74354,9 @@
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $858万
-$22,636/呎
+$22,696/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -74433,9 +74433,9 @@
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $854万
-$22,541/呎
+$22,601/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -74512,9 +74512,9 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $885万
-$23,351/呎
+$23,413/呎
 (19年-11月-13日)</t>
         </is>
       </c>
@@ -74670,9 +74670,9 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $900万
-$23,739/呎
+$23,801/呎
 (19年-11月-06日)</t>
         </is>
       </c>
@@ -74907,9 +74907,9 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $833万
-$21,977/呎
+$22,035/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -74986,9 +74986,9 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $837万
-$22,082/呎
+$22,141/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -75065,9 +75065,9 @@
       </c>
       <c r="I22" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $838万
-$22,120/呎
+$22,178/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -75223,9 +75223,9 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $823万
-$21,713/呎
+$21,771/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -75302,9 +75302,9 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $831万
-$21,921/呎
+$21,979/呎
 (19年-10月-28日)</t>
         </is>
       </c>
@@ -75381,9 +75381,9 @@
       </c>
       <c r="I26" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $818万
-$21,580/呎
+$21,638/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -75539,9 +75539,9 @@
       </c>
       <c r="I28" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $853万
-$22,501/呎
+$22,561/呎
 (19年-11月-13日)</t>
         </is>
       </c>
@@ -75562,9 +75562,9 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3394万
-$27,777/呎
+$27,800/呎
 (19年-11月-20日)</t>
         </is>
       </c>
@@ -75618,9 +75618,9 @@
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $831万
-$21,913/呎
+$21,971/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -75641,9 +75641,9 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3309万
-$27,078/呎
+$27,101/呎
 (19年-11月-13日)</t>
         </is>
       </c>
@@ -75697,9 +75697,9 @@
       </c>
       <c r="I30" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $805万
-$21,236/呎
+$21,293/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -75720,9 +75720,9 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3223万
-$26,378/呎
+$26,400/呎
 (19年-11月-12日)</t>
         </is>
       </c>
@@ -75776,9 +75776,9 @@
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $801万
-$21,127/呎
+$21,183/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -75799,9 +75799,9 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3230万
-$26,432/呎
+$26,454/呎
 (19年-11月-22日)</t>
         </is>
       </c>
@@ -75878,9 +75878,9 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3249万
-$26,586/呎
+$26,608/呎
 (19年-12月-17日)</t>
         </is>
       </c>
@@ -76036,9 +76036,9 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3229万
-$26,422/呎
+$26,444/呎
 (20年-10月-16日)</t>
         </is>
       </c>
@@ -76092,9 +76092,9 @@
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $785万
-$20,704/呎
+$20,759/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -76115,9 +76115,9 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3193万
-$26,129/呎
+$26,150/呎
 (20年-02月-06日)</t>
         </is>
       </c>
@@ -76171,9 +76171,9 @@
       </c>
       <c r="I36" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $800万
-$21,118/呎
+$21,174/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -76250,9 +76250,9 @@
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $808万
-$21,325/呎
+$21,381/呎
 (19年-11月-07日)</t>
         </is>
       </c>
@@ -76408,9 +76408,9 @@
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $773万
-$20,394/呎
+$20,448/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -76431,9 +76431,9 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $3130万
-$25,614/呎
+$25,635/呎
 (20年-12月-30日)</t>
         </is>
       </c>
@@ -76487,9 +76487,9 @@
       </c>
       <c r="I40" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $1020万
-$26,912/呎
+$26,983/呎
 (26年-06月-02日)</t>
         </is>
       </c>
@@ -76566,9 +76566,9 @@
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $823万
-$21,709/呎
+$21,766/呎
 (19年-11月-05日)</t>
         </is>
       </c>
@@ -76589,9 +76589,9 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $2980万
-$24,386/呎
+$24,406/呎
 (19年-11月-11日)</t>
         </is>
       </c>
@@ -76645,9 +76645,9 @@
       </c>
       <c r="I42" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $802万
-$21,152/呎
+$21,208/呎
 (19年-11月-04日)</t>
         </is>
       </c>
@@ -76724,9 +76724,9 @@
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $780万
-$20,568/呎
+$20,622/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -76803,9 +76803,9 @@
       </c>
       <c r="I44" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $779万
-$20,547/呎
+$20,601/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -76826,9 +76826,9 @@
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>A | 1222呎 (4+房)
+          <t>A | 1221呎 (4+房)
 $2930万
-$23,977/呎
+$23,997/呎
 (19年-11月-15日)</t>
         </is>
       </c>
@@ -76882,9 +76882,9 @@
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $765万
-$20,191/呎
+$20,244/呎
 (19年-10月-22日)</t>
         </is>
       </c>
@@ -76961,9 +76961,9 @@
       </c>
       <c r="I46" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $767万
-$20,249/呎
+$20,302/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -77040,9 +77040,9 @@
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $776万
-$20,485/呎
+$20,539/呎
 (19年-10月-21日)</t>
         </is>
       </c>
@@ -77119,9 +77119,9 @@
       </c>
       <c r="I48" s="21" t="inlineStr">
         <is>
-          <t>H | 379呎 (1房)
+          <t>H | 378呎 (1房)
 $785万
-$20,718/呎
+$20,773/呎
 (19年-10月-21日)</t>
         </is>
       </c>
@@ -77307,9 +77307,9 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $5380万
-$35,535/呎
+$35,558/呎
 (19年-11月-18日)</t>
         </is>
       </c>
@@ -77331,9 +77331,9 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1589万
-$30,158/呎
+$30,101/呎
 (19年-11月-15日)</t>
         </is>
       </c>
@@ -77497,9 +77497,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $5311万
-$35,077/呎
+$35,100/呎
 (20年-10月-22日)</t>
         </is>
       </c>
@@ -77545,9 +77545,9 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $859万
-$24,468/呎
+$24,538/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -77592,9 +77592,9 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $5220万
-$34,477/呎
+$34,500/呎
 (20年-11月-13日)</t>
         </is>
       </c>
@@ -77616,9 +77616,9 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1579万
-$29,960/呎
+$29,903/呎
 (19年-11月-15日)</t>
         </is>
       </c>
@@ -77640,9 +77640,9 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $828万
-$23,598/呎
+$23,666/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -77687,9 +77687,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $5190万
-$34,277/呎
+$34,300/呎
 (20年-11月-13日)</t>
         </is>
       </c>
@@ -77711,9 +77711,9 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1569万
-$29,767/呎
+$29,711/呎
 (19年-11月-13日)</t>
         </is>
       </c>
@@ -77735,9 +77735,9 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $832万
-$23,697/呎
+$23,765/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -77782,9 +77782,9 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $5749万
-$37,975/呎
+$38,000/呎
 (21年-09月-24日)</t>
         </is>
       </c>
@@ -77830,9 +77830,9 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $825万
-$23,501/呎
+$23,568/呎
 (19年-10月-22日)</t>
         </is>
       </c>
@@ -77877,9 +77877,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $5436万
-$35,905/呎
+$35,929/呎
 (20年-12月-08日)</t>
         </is>
       </c>
@@ -77925,9 +77925,9 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $815万
-$23,206/呎
+$23,273/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -78020,9 +78020,9 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $811万
-$23,106/呎
+$23,172/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -78091,9 +78091,9 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1486万
-$28,196/呎
+$28,142/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -78257,9 +78257,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4344万
-$28,691/呎
+$28,710/呎
 (19年-10月-23日)</t>
         </is>
       </c>
@@ -78281,9 +78281,9 @@
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1468万
-$27,856/呎
+$27,803/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -78305,9 +78305,9 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $801万
-$22,817/呎
+$22,882/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -78352,9 +78352,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4327万
-$28,577/呎
+$28,596/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -78376,9 +78376,9 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1553万
-$29,472/呎
+$29,416/呎
 (19年-11月-11日)</t>
         </is>
       </c>
@@ -78400,9 +78400,9 @@
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $794万
-$22,633/呎
+$22,698/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -78447,9 +78447,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4221万
-$27,880/呎
+$27,898/呎
 (19年-10月-21日)</t>
         </is>
       </c>
@@ -78495,9 +78495,9 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $794万
-$22,633/呎
+$22,698/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -78542,9 +78542,9 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4244万
-$28,032/呎
+$28,051/呎
 (19年-10月-25日)</t>
         </is>
       </c>
@@ -78590,9 +78590,9 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $793万
-$22,582/呎
+$22,646/呎
 (19年-10月-08日)</t>
         </is>
       </c>
@@ -78685,9 +78685,9 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $807万
-$22,996/呎
+$23,061/呎
 (19年-10月-08日)</t>
         </is>
       </c>
@@ -78780,9 +78780,9 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $788万
-$22,447/呎
+$22,511/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -78875,9 +78875,9 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $782万
-$22,291/呎
+$22,355/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -78922,9 +78922,9 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4126万
-$27,254/呎
+$27,272/呎
 (19年-09月-26日)</t>
         </is>
       </c>
@@ -78946,9 +78946,9 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1424万
-$27,022/呎
+$26,971/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -79065,9 +79065,9 @@
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $781万
-$22,247/呎
+$22,310/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -79136,9 +79136,9 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1433万
-$27,186/呎
+$27,135/呎
 (19年-10月-23日)</t>
         </is>
       </c>
@@ -79160,9 +79160,9 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $778万
-$22,174/呎
+$22,237/呎
 (19年-10月-23日)</t>
         </is>
       </c>
@@ -79215,9 +79215,9 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $948万
-$26,324/呎
+$26,398/呎
 (19年-10月-22日)</t>
         </is>
       </c>
@@ -79255,9 +79255,9 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $783万
-$22,309/呎
+$22,373/呎
 (19年-10月-22日)</t>
         </is>
       </c>
@@ -79302,9 +79302,9 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $4118万
-$27,144/呎
+$27,180/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -79326,9 +79326,9 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1487万
-$28,216/呎
+$28,162/呎
 (19年-11月-13日)</t>
         </is>
       </c>
@@ -79350,9 +79350,9 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $786万
-$22,389/呎
+$22,453/呎
 (19年-10月-11日)</t>
         </is>
       </c>
@@ -79397,17 +79397,17 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $4016万
-$26,475/呎
+$26,510/呎
 (19年-10月-16日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $955万
-$26,520/呎
+$26,594/呎
 (19年-10月-28日)</t>
         </is>
       </c>
@@ -79421,9 +79421,9 @@
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1430万
-$27,134/呎
+$27,082/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -79500,9 +79500,9 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $1041万
-$28,920/呎
+$29,001/呎
 (21年-10月-19日)</t>
         </is>
       </c>
@@ -79516,9 +79516,9 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1559万
-$29,576/呎
+$29,520/呎
 (21年-11月-08日)</t>
         </is>
       </c>
@@ -79540,9 +79540,9 @@
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $771万
-$21,964/呎
+$22,027/呎
 (19年-10月-10日)</t>
         </is>
       </c>
@@ -79587,9 +79587,9 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $4030万
-$26,564/呎
+$26,600/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -79635,9 +79635,9 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $760万
-$21,666/呎
+$21,727/呎
 (19年-10月-14日)</t>
         </is>
       </c>
@@ -79682,9 +79682,9 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $4004万
-$26,392/呎
+$26,427/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -79730,9 +79730,9 @@
       </c>
       <c r="H30" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $757万
-$21,556/呎
+$21,618/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -79801,9 +79801,9 @@
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1427万
-$27,074/呎
+$27,023/呎
 (19年-11月-04日)</t>
         </is>
       </c>
@@ -79825,9 +79825,9 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $760万
-$21,648/呎
+$21,710/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -79880,9 +79880,9 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $906万
-$25,164/呎
+$25,234/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -79896,9 +79896,9 @@
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1357万
-$25,747/呎
+$25,699/呎
 (19年-10月-23日)</t>
         </is>
       </c>
@@ -79967,9 +79967,9 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $3921万
-$25,846/呎
+$25,880/呎
 (19年-10月-25日)</t>
         </is>
       </c>
@@ -79991,9 +79991,9 @@
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1324万
-$25,121/呎
+$25,073/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -80015,9 +80015,9 @@
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $760万
-$21,663/呎
+$21,725/呎
 (19年-10月-23日)</t>
         </is>
       </c>
@@ -80062,9 +80062,9 @@
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $3815万
-$25,150/呎
+$25,183/呎
 (20年-05月-05日)</t>
         </is>
       </c>
@@ -80086,9 +80086,9 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1324万
-$25,121/呎
+$25,073/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -80157,17 +80157,17 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $3756万
-$24,758/呎
+$24,791/呎
 (19年-12月-23日)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $873万
-$24,261/呎
+$24,329/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -80205,9 +80205,9 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $776万
-$22,095/呎
+$22,158/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -80252,17 +80252,17 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $3743万
-$24,674/呎
+$24,706/呎
 (20年-12月-10日)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $863万
-$23,969/呎
+$24,035/呎
 (19年-10月-21日)</t>
         </is>
       </c>
@@ -80300,9 +80300,9 @@
       </c>
       <c r="H36" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $750万
-$21,369/呎
+$21,430/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -80371,9 +80371,9 @@
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1331万
-$25,253/呎
+$25,205/呎
 (19年-11月-04日)</t>
         </is>
       </c>
@@ -80395,9 +80395,9 @@
       </c>
       <c r="H37" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $740万
-$21,080/呎
+$21,140/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -80450,9 +80450,9 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $839万
-$23,296/呎
+$23,360/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -80490,9 +80490,9 @@
       </c>
       <c r="H38" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $764万
-$21,759/呎
+$21,821/呎
 (19年-10月-21日)</t>
         </is>
       </c>
@@ -80545,9 +80545,9 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $822万
-$22,824/呎
+$22,887/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -80585,9 +80585,9 @@
       </c>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $754万
-$21,486/呎
+$21,548/呎
 (19年-09月-19日)</t>
         </is>
       </c>
@@ -80632,17 +80632,17 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $3681万
-$24,268/呎
+$24,300/呎
 (21年-02月-03日)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $822万
-$22,832/呎
+$22,896/呎
 (19年-10月-21日)</t>
         </is>
       </c>
@@ -80656,9 +80656,9 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1216万
-$23,071/呎
+$23,028/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -80680,9 +80680,9 @@
       </c>
       <c r="H40" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $747万
-$21,283/呎
+$21,344/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -80775,9 +80775,9 @@
       </c>
       <c r="H41" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $752万
-$21,419/呎
+$21,481/呎
 (19年-10月-22日)</t>
         </is>
       </c>
@@ -80822,17 +80822,17 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $3828万
-$25,233/呎
+$25,267/呎
 (21年-09月-16日)</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $812万
-$22,556/呎
+$22,619/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -80917,17 +80917,17 @@
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $3646万
-$24,034/呎
+$24,066/呎
 (21年-05月-27日)</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $792万
-$22,006/呎
+$22,067/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -81012,17 +81012,17 @@
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>A | 1517呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $4001万
-$26,373/呎
+$26,408/呎
 (21年-12月-09日)</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>B | 360呎 (1房)
+          <t>B | 359呎 (1房)
 $802万
-$22,288/呎
+$22,350/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -81036,9 +81036,9 @@
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
-          <t>D | 527呎 (2房)
+          <t>D | 528呎 (2房)
 $1197万
-$22,715/呎
+$22,672/呎
 (19年-10月-24日)</t>
         </is>
       </c>
@@ -81060,9 +81060,9 @@
       </c>
       <c r="H44" s="21" t="inlineStr">
         <is>
-          <t>G | 351呎 (1房)
+          <t>G | 350呎 (1房)
 $741万
-$21,110/呎
+$21,171/呎
 (19年-10月-14日)</t>
         </is>
       </c>
@@ -81270,17 +81270,17 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1288万
-$30,887/呎
+$30,962/呎
 (25年-11月-07日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $701万
-$25,388/呎
+$25,480/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -81325,9 +81325,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $5680万
-$37,517/呎
+$37,541/呎
 (21年-06月-15日)</t>
         </is>
       </c>
@@ -81412,9 +81412,9 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1310万
-$31,421/呎
+$31,496/呎
 (21年-05月-04日)</t>
         </is>
       </c>
@@ -81483,9 +81483,9 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1310万
-$31,421/呎
+$31,496/呎
 (21年-04月-08日)</t>
         </is>
       </c>
@@ -81554,17 +81554,17 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1302万
-$31,223/呎
+$31,298/呎
 (21年-01月-05日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $685万
-$24,829/呎
+$24,919/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -81625,17 +81625,17 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1445万
-$34,645/呎
+$34,728/呎
 (21年-10月-20日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $677万
-$24,544/呎
+$24,633/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -81696,9 +81696,9 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1310万
-$31,413/呎
+$31,489/呎
 (21年-03月-14日)</t>
         </is>
       </c>
@@ -81751,9 +81751,9 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4345万
-$28,696/呎
+$28,715/呎
 (19年-10月-25日)</t>
         </is>
       </c>
@@ -81775,9 +81775,9 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $672万
-$24,341/呎
+$24,430/呎
 (19年-10月-10日)</t>
         </is>
       </c>
@@ -81838,17 +81838,17 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1285万
-$30,824/呎
+$30,898/呎
 (21年-04月-09日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $674万
-$24,417/呎
+$24,506/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -81893,9 +81893,9 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4278万
-$28,258/呎
+$28,277/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -81909,9 +81909,9 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1320万
-$31,651/呎
+$31,727/呎
 (21年-06月-09日)</t>
         </is>
       </c>
@@ -81964,9 +81964,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4293万
-$28,355/呎
+$28,374/呎
 (19年-10月-21日)</t>
         </is>
       </c>
@@ -82051,9 +82051,9 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1311万
-$31,447/呎
+$31,523/呎
 (21年-06月-10日)</t>
         </is>
       </c>
@@ -82106,9 +82106,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4115万
-$27,182/呎
+$27,200/呎
 (24年-12月-10日)</t>
         </is>
       </c>
@@ -82122,17 +82122,17 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1335万
-$32,005/呎
+$32,082/呎
 (21年-09月-28日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $663万
-$24,004/呎
+$24,092/呎
 (19年-10月-14日)</t>
         </is>
       </c>
@@ -82193,17 +82193,17 @@
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1263万
-$30,290/呎
+$30,362/呎
 (20年-12月-18日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $657万
-$23,788/呎
+$23,874/呎
 (19年-10月-10日)</t>
         </is>
       </c>
@@ -82264,17 +82264,17 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1262万
-$30,275/呎
+$30,348/呎
 (21年-04月-19日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $671万
-$24,316/呎
+$24,404/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -82319,9 +82319,9 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4134万
-$27,304/呎
+$27,322/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -82335,17 +82335,17 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1259万
-$30,191/呎
+$30,263/呎
 (21年-05月-21日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $653万
-$23,646/呎
+$23,732/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -82406,17 +82406,17 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1435万
-$34,417/呎
+$34,500/呎
 (21年-12月-16日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $659万
-$23,870/呎
+$23,957/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -82477,17 +82477,17 @@
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1263万
-$30,286/呎
+$30,359/呎
 (20年-12月-23日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $649万
-$23,501/呎
+$23,586/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -82532,9 +82532,9 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4262万
-$28,149/呎
+$28,168/呎
 (19年-10月-23日)</t>
         </is>
       </c>
@@ -82548,17 +82548,17 @@
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1245万
-$29,855/呎
+$29,927/呎
 (21年-02月-03日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $655万
-$23,726/呎
+$23,812/呎
 (19年-10月-14日)</t>
         </is>
       </c>
@@ -82603,9 +82603,9 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4055万
-$26,782/呎
+$26,800/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -82619,17 +82619,17 @@
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1240万
-$29,730/呎
+$29,802/呎
 (20年-12月-15日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $645万
-$23,359/呎
+$23,444/呎
 (19年-10月-11日)</t>
         </is>
       </c>
@@ -82690,17 +82690,17 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1235万
-$29,606/呎
+$29,677/呎
 (21年-04月-27日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $643万
-$23,292/呎
+$23,377/呎
 (19年-10月-14日)</t>
         </is>
       </c>
@@ -82745,9 +82745,9 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4034万
-$26,641/呎
+$26,659/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -82769,9 +82769,9 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $643万
-$23,292/呎
+$23,377/呎
 (19年-10月-08日)</t>
         </is>
       </c>
@@ -82832,9 +82832,9 @@
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1237万
-$29,675/呎
+$29,746/呎
 (21年-02月-08日)</t>
         </is>
       </c>
@@ -82887,9 +82887,9 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $4176万
-$27,583/呎
+$27,601/呎
 (20年-10月-23日)</t>
         </is>
       </c>
@@ -82903,17 +82903,17 @@
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1231万
-$29,527/呎
+$29,598/呎
 (20年-12月-17日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $633万
-$22,938/呎
+$23,022/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -82974,17 +82974,17 @@
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1203万
-$28,839/呎
+$28,909/呎
 (21年-03月-31日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $646万
-$23,397/呎
+$23,483/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -83029,9 +83029,9 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3922万
-$25,904/呎
+$25,921/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -83045,17 +83045,17 @@
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1210万
-$29,018/呎
+$29,088/呎
 (21年-01月-21日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $642万
-$23,279/呎
+$23,363/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -83100,9 +83100,9 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3974万
-$26,250/呎
+$26,268/呎
 (19年-09月-26日)</t>
         </is>
       </c>
@@ -83116,17 +83116,17 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1203万
-$28,838/呎
+$28,908/呎
 (21年-06月-08日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $629万
-$22,777/呎
+$22,860/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -83171,9 +83171,9 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3871万
-$25,567/呎
+$25,584/呎
 (19年-10月-17日)</t>
         </is>
       </c>
@@ -83187,17 +83187,17 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1201万
-$28,801/呎
+$28,870/呎
 (20年-12月-22日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $617万
-$22,372/呎
+$22,453/呎
 (19年-10月-10日)</t>
         </is>
       </c>
@@ -83258,17 +83258,17 @@
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1161万
-$27,831/呎
+$27,898/呎
 (21年-05月-14日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $633万
-$22,931/呎
+$23,014/呎
 (19年-10月-10日)</t>
         </is>
       </c>
@@ -83313,9 +83313,9 @@
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3967万
-$26,199/呎
+$26,217/呎
 (19年-11月-05日)</t>
         </is>
       </c>
@@ -83329,17 +83329,17 @@
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1161万
-$27,831/呎
+$27,898/呎
 (21年-03月-31日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $622万
-$22,540/呎
+$22,622/呎
 (19年-09月-19日)</t>
         </is>
       </c>
@@ -83384,9 +83384,9 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3856万
-$25,472/呎
+$25,489/呎
 (19年-10月-25日)</t>
         </is>
       </c>
@@ -83400,17 +83400,17 @@
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1208万
-$28,963/呎
+$29,033/呎
 (21年-08月-19日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $614万
-$22,254/呎
+$22,335/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -83479,9 +83479,9 @@
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $629万
-$22,794/呎
+$22,877/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -83542,17 +83542,17 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1179万
-$28,278/呎
+$28,346/呎
 (21年-07月-02日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $610万
-$22,102/呎
+$22,183/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -83597,9 +83597,9 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3730万
-$24,637/呎
+$24,653/呎
 (21年-03月-30日)</t>
         </is>
       </c>
@@ -83613,17 +83613,17 @@
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1089万
-$26,127/呎
+$26,189/呎
 (20年-12月-24日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $612万
-$22,185/呎
+$22,265/呎
 (19年-10月-15日)</t>
         </is>
       </c>
@@ -83668,9 +83668,9 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3664万
-$24,202/呎
+$24,218/呎
 (19年-10月-18日)</t>
         </is>
       </c>
@@ -83692,9 +83692,9 @@
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $612万
-$22,164/呎
+$22,245/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -83755,17 +83755,17 @@
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1077万
-$25,825/呎
+$25,887/呎
 (20年-12月-17日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $611万
-$22,141/呎
+$22,222/呎
 (19年-10月-14日)</t>
         </is>
       </c>
@@ -83826,17 +83826,17 @@
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1124万
-$26,947/呎
+$27,012/呎
 (21年-07月-23日)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $611万
-$22,121/呎
+$22,201/呎
 (19年-10月-10日)</t>
         </is>
       </c>
@@ -83897,17 +83897,17 @@
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1067万
-$25,586/呎
+$25,647/呎
 (21年-03月-03日)</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $610万
-$22,098/呎
+$22,178/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -83952,9 +83952,9 @@
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3782万
-$24,983/呎
+$25,000/呎
 (21年-08月-24日)</t>
         </is>
       </c>
@@ -83968,17 +83968,17 @@
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1070万
-$25,656/呎
+$25,717/呎
 (21年-05月-27日)</t>
         </is>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $609万
-$22,078/呎
+$22,158/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -84023,9 +84023,9 @@
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>A | 1514呎 (4+房)
+          <t>A | 1513呎 (4+房)
 $3432万
-$22,665/呎
+$22,680/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -84039,17 +84039,17 @@
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>C | 417呎 (2房)
+          <t>C | 416呎 (2房)
 $1051万
-$25,214/呎
+$25,275/呎
 (21年-03月-30日)</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
-          <t>D | 276呎 (开放式)
+          <t>D | 275呎 (开放式)
 $614万
-$22,232/呎
+$22,313/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -84228,9 +84228,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1573呎 (3房)
+          <t>A | 1629呎 (3房)
 $4806万
-$30,550/呎
+$29,500/呎
 (22年-07月-26日)</t>
         </is>
       </c>
@@ -84274,9 +84274,9 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1573呎 (3房)
+          <t>A | 1629呎 (3房)
 $4708万
-$29,929/呎
+$28,900/呎
 (21年-08月-04日)</t>
         </is>
       </c>
@@ -84408,17 +84408,17 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 2112呎 (4+房)
+          <t>A | 2171呎 (4+房)
 $6144万
-$29,091/呎
+$28,300/呎
 (26年-06月-04日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1584呎 (3房)
+          <t>B | 1640呎 (3房)
 $4592万
-$28,990/呎
+$28,000/呎
 (26年-05月-28日)</t>
         </is>
       </c>
@@ -84431,17 +84431,17 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 2112呎 (4+房)
+          <t>A | 2171呎 (4+房)
 $5428万
-$25,698/呎
+$25,000/呎
 (25年-07月-03日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 1584呎 (3房)
+          <t>B | 1640呎 (3房)
 $4875万
-$30,776/呎
+$29,725/呎
 (21年-08月-24日)</t>
         </is>
       </c>
@@ -84477,9 +84477,9 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 2112呎 (4+房)
+          <t>A | 2171呎 (4+房)
 $6470万
-$30,634/呎
+$29,802/呎
 (21年-12月-10日)</t>
         </is>
       </c>
